--- a/Data for R/Delta Smelt Diet Station Lookup_NKU07Apr2026_v2.xlsx
+++ b/Data for R/Delta Smelt Diet Station Lookup_NKU07Apr2026_v2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cawater-my.sharepoint.com/personal/christina_burdi_water_ca_gov/Documents/Documents/Current Data/EDI Data Posting/Delta Smelt/R/Data for R/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cawater-my.sharepoint.com/personal/christina_burdi_water_ca_gov/Documents/Documents/Current Data/EDI Data Posting/Delta Smelt/R/Delta Smelt Diet/Data for R/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{B8E43E85-AC74-4EEF-8305-63AEC1973FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F8562DE-07B3-4012-9466-AE43A3095CAF}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{B8E43E85-AC74-4EEF-8305-63AEC1973FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EB71C8E-641A-4338-9E5D-8BB5917C2CCE}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{95307E76-F392-4E9E-BA40-7857CC176927}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{95307E76-F392-4E9E-BA40-7857CC176927}"/>
   </bookViews>
   <sheets>
     <sheet name="Delta Smelt Diet Station Lookup" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="302">
   <si>
     <t>Project</t>
   </si>
@@ -942,22 +942,13 @@
   </si>
   <si>
     <t>South Delta</t>
-  </si>
-  <si>
-    <t>delete; fish ID'd as WAKASA in EDSM EDI data</t>
-  </si>
-  <si>
-    <t>no coordinates in DJFMP EDI file; check w/ CEB</t>
-  </si>
-  <si>
-    <t>Notes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1088,6 +1079,12 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1436,9 +1433,9 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="8"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="7"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="8" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1814,1654 +1811,1653 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D9997D-EAA0-4A05-B4A9-5D253C96E35F}">
-  <dimension ref="A1:G368"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F368"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="34.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="34.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>38.332430000000002</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>-121.64794000000001</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>38.064950000000003</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>-122.03767000000001</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>38.06597</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>-121.97063</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>38.047710000000002</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>-121.89447</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>38.132390000000001</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>-122.05826999999999</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>38.386450000000004</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>-121.62388</v>
       </c>
-      <c r="F7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="F7" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>38.049010000000003</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>-121.84439</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>38.052309999999999</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>-121.87038</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>38.112780000000001</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>-122.05582</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>38.082149999999999</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>-122.04040999999999</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>38.395240000000001</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>-121.61968</v>
       </c>
-      <c r="F12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="F12" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>38.069540000000003</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>-121.84788</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>38.065620000000003</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>-122.02305</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>38.058239999999998</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>-121.87255999999999</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>38.062049999999999</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>-122.00064999999999</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>38.099939999999997</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>-122.06793</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>38.055810000000001</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="1">
         <v>-121.96093</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>38.060470000000002</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>-122.04606</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>38.094099999999997</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>-122.05947999999999</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="1">
         <v>38.071060000000003</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="1">
         <v>-122.01783</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="1">
         <v>38.067900000000002</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="1">
         <v>-121.84983</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="1">
         <v>38.053840000000001</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="1">
         <v>-121.86936</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="1">
         <v>38.094920000000002</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="1">
         <v>-122.05696</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="1">
         <v>38.16527</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="1">
         <v>-122.04295999999999</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" t="s">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="1">
         <v>38.056460000000001</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="1">
         <v>-121.87784000000001</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>6</v>
-      </c>
-      <c r="B27" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="1">
         <v>38.071579999999997</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="1">
         <v>-121.98428</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" t="s">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="1">
         <v>38.05988</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="1">
         <v>-121.99809999999999</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="1">
         <v>38.064979999999998</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="1">
         <v>-121.86378000000001</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="1">
         <v>38.076009999999997</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="1">
         <v>-121.77203</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="1">
         <v>38.067790000000002</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="1">
         <v>-121.83365999999999</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="1">
         <v>38.174410000000002</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="1">
         <v>-121.96326999999999</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="1">
         <v>38.176909999999999</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="1">
         <v>-122.00949</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="1">
         <v>38.048259999999999</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="1">
         <v>-121.89879999999999</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="1">
         <v>38.071019999999997</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="1">
         <v>-121.84818</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="1">
         <v>38.1736</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="1">
         <v>-121.94748</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>6</v>
-      </c>
-      <c r="B37" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="1">
         <v>38.06176</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="1">
         <v>-121.7903</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>6</v>
-      </c>
-      <c r="B38" t="s">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="1">
         <v>38.070300000000003</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="1">
         <v>-121.83148</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="1">
         <v>38.045520000000003</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="1">
         <v>-121.92586</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>6</v>
-      </c>
-      <c r="B40" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="1">
         <v>38.083860000000001</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="1">
         <v>-121.99911</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="1">
         <v>38.185789999999997</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="1">
         <v>-121.96987</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>6</v>
-      </c>
-      <c r="B42" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="1">
         <v>38.046810000000001</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="1">
         <v>-121.89945</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>6</v>
-      </c>
-      <c r="B43" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="1">
         <v>38.395699999999998</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="1">
         <v>-121.61897999999999</v>
       </c>
-      <c r="F43" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44" t="s">
+      <c r="F43" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="1">
         <v>38.422170000000001</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="1">
         <v>-121.60751999999999</v>
       </c>
-      <c r="F44" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>6</v>
-      </c>
-      <c r="B45" t="s">
+      <c r="F44" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="1">
         <v>38.064160000000001</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="1">
         <v>-121.85348</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>6</v>
-      </c>
-      <c r="B46" t="s">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="1">
         <v>38.055140000000002</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="1">
         <v>-121.94020999999999</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="1">
         <v>38.447319999999998</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="1">
         <v>-121.59549</v>
       </c>
-      <c r="F47" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>6</v>
-      </c>
-      <c r="B48" t="s">
+      <c r="F47" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="1">
         <v>38.422910000000002</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="1">
         <v>-121.60767</v>
       </c>
-      <c r="F48" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>6</v>
-      </c>
-      <c r="B49" t="s">
+      <c r="F48" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="1">
         <v>38.42501</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="1">
         <v>-121.60663</v>
       </c>
-      <c r="F49" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>6</v>
-      </c>
-      <c r="B50" t="s">
+      <c r="F49" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="1">
         <v>38.302</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="1">
         <v>-121.65506999999999</v>
       </c>
-      <c r="F50" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>6</v>
-      </c>
-      <c r="B51" t="s">
+      <c r="F50" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="1">
         <v>38.421030000000002</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="1">
         <v>-121.60749</v>
       </c>
-      <c r="F51" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>6</v>
-      </c>
-      <c r="B52" t="s">
+      <c r="F51" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="1">
         <v>38.467979999999997</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="1">
         <v>-121.58647999999999</v>
       </c>
-      <c r="F52" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>6</v>
-      </c>
-      <c r="B53" t="s">
+      <c r="F52" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="1">
         <v>38.485860000000002</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="1">
         <v>-121.58477000000001</v>
       </c>
-      <c r="F53" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>6</v>
-      </c>
-      <c r="B54" t="s">
+      <c r="F53" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="1">
         <v>38.385779999999997</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="1">
         <v>-121.62494</v>
       </c>
-      <c r="F54" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>6</v>
-      </c>
-      <c r="B55" t="s">
+      <c r="F54" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="1">
         <v>38.067599999999999</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="1">
         <v>-121.82185</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F55" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>6</v>
-      </c>
-      <c r="B56" t="s">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="1">
         <v>38.370370000000001</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="1">
         <v>-121.63151999999999</v>
       </c>
-      <c r="F56" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>6</v>
-      </c>
-      <c r="B57" t="s">
+      <c r="F56" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="1">
         <v>38.172400000000003</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="1">
         <v>-122.06511999999999</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F57" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>6</v>
-      </c>
-      <c r="B58" t="s">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="1">
         <v>38.165509999999998</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="1">
         <v>-122.04404</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F58" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>6</v>
-      </c>
-      <c r="B59" t="s">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="1">
         <v>38.108800000000002</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="1">
         <v>-122.05777</v>
       </c>
-      <c r="F59" t="s">
+      <c r="F59" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>6</v>
-      </c>
-      <c r="B60" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="1">
         <v>38.066400000000002</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="1">
         <v>-121.81958</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F60" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>6</v>
-      </c>
-      <c r="B61" t="s">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="1">
         <v>38.063569999999999</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="1">
         <v>-121.81663</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F61" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>6</v>
-      </c>
-      <c r="B62" t="s">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="1">
         <v>38.401009999999999</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="1">
         <v>-121.61781999999999</v>
       </c>
-      <c r="F62" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>6</v>
-      </c>
-      <c r="B63" t="s">
+      <c r="F62" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="1">
         <v>38.34796</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="1">
         <v>-121.64151</v>
       </c>
-      <c r="F63" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>6</v>
-      </c>
-      <c r="B64" t="s">
+      <c r="F63" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="1">
         <v>38.180480000000003</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="1">
         <v>-122.00072</v>
       </c>
-      <c r="F64" t="s">
+      <c r="F64" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>6</v>
-      </c>
-      <c r="B65" t="s">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="1">
         <v>38.32902</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="1">
         <v>-121.64791</v>
       </c>
-      <c r="F65" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>6</v>
-      </c>
-      <c r="B66" t="s">
+      <c r="F65" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="1">
         <v>38.099429999999998</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="1">
         <v>-122.06699</v>
       </c>
-      <c r="F66" t="s">
+      <c r="F66" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>6</v>
-      </c>
-      <c r="B67" t="s">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="1">
         <v>38.185630000000003</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="1">
         <v>-122.05531000000001</v>
       </c>
-      <c r="F67" t="s">
+      <c r="F67" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>6</v>
-      </c>
-      <c r="B68" t="s">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="1">
         <v>38.356479999999998</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="1">
         <v>-121.63838</v>
       </c>
-      <c r="F68" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>6</v>
-      </c>
-      <c r="B69" t="s">
+      <c r="F68" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="1">
         <v>38.376109999999997</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="1">
         <v>-121.62819</v>
       </c>
-      <c r="F69" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>6</v>
-      </c>
-      <c r="B70" t="s">
+      <c r="F69" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="1">
         <v>38.069510000000001</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="1">
         <v>-121.83338000000001</v>
       </c>
-      <c r="F70" t="s">
+      <c r="F70" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>6</v>
-      </c>
-      <c r="B71" t="s">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="1">
         <v>38.345500000000001</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="1">
         <v>-121.64266000000001</v>
       </c>
-      <c r="F71" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>6</v>
-      </c>
-      <c r="B72" t="s">
+      <c r="F71" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="1">
         <v>38.07056</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="1">
         <v>-121.83604</v>
       </c>
-      <c r="F72" t="s">
+      <c r="F72" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>6</v>
-      </c>
-      <c r="B73" t="s">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="1">
         <v>38.39376</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="1">
         <v>-121.62058</v>
       </c>
-      <c r="F73" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>6</v>
-      </c>
-      <c r="B74" t="s">
+      <c r="F73" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="1">
         <v>38.366370000000003</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="1">
         <v>-121.63373</v>
       </c>
-      <c r="F74" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>6</v>
-      </c>
-      <c r="B75" t="s">
+      <c r="F74" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="1">
         <v>38.389760000000003</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="1">
         <v>-121.62311</v>
       </c>
-      <c r="F75" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>6</v>
-      </c>
-      <c r="B76" t="s">
+      <c r="F75" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="1">
         <v>38.059399999999997</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="1">
         <v>-121.80822999999999</v>
       </c>
-      <c r="F76" t="s">
+      <c r="F76" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B77" t="s">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="1">
         <v>38.40793</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="1">
         <v>-121.61381</v>
       </c>
-      <c r="F77" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
-        <v>6</v>
-      </c>
-      <c r="B78" t="s">
+      <c r="F77" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="1">
         <v>38.427689999999998</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="1">
         <v>-121.60460999999999</v>
       </c>
-      <c r="F78" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>6</v>
-      </c>
-      <c r="B79" t="s">
+      <c r="F78" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="1">
         <v>38.4574</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="1">
         <v>-121.59063999999999</v>
       </c>
-      <c r="F79" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>6</v>
-      </c>
-      <c r="B80" t="s">
+      <c r="F79" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="1">
         <v>38.386240000000001</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="1">
         <v>-121.62434</v>
       </c>
-      <c r="F80" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
-        <v>6</v>
-      </c>
-      <c r="B81" t="s">
+      <c r="F80" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="1">
         <v>38.089370000000002</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="1">
         <v>-121.74326000000001</v>
       </c>
-      <c r="F81" t="s">
+      <c r="F81" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B82" t="s">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="1">
         <v>38.065890000000003</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="1">
         <v>-121.81555</v>
       </c>
-      <c r="F82" t="s">
+      <c r="F82" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
-        <v>6</v>
-      </c>
-      <c r="B83" t="s">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="1">
         <v>38.469900000000003</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="1">
         <v>-121.58547</v>
       </c>
-      <c r="F83" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
-        <v>6</v>
-      </c>
-      <c r="B84" t="s">
+      <c r="F83" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="1">
         <v>38.414569999999998</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="1">
         <v>-121.61108</v>
       </c>
-      <c r="F84" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
-        <v>6</v>
-      </c>
-      <c r="B85" t="s">
+      <c r="F84" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="1">
         <v>38.485759999999999</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="1">
         <v>-121.58450000000001</v>
       </c>
-      <c r="F85" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>6</v>
-      </c>
-      <c r="B86" t="s">
+      <c r="F85" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="1">
         <v>38.440460000000002</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="1">
         <v>-121.59932000000001</v>
       </c>
-      <c r="F86" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
-        <v>6</v>
-      </c>
-      <c r="B87" t="s">
+      <c r="F86" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="1">
         <v>38.175449999999998</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="1">
         <v>-122.01299</v>
       </c>
-      <c r="F87" t="s">
+      <c r="F87" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
-        <v>6</v>
-      </c>
-      <c r="B88" t="s">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="1">
         <v>38.193919999999999</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="1">
         <v>-122.04002</v>
       </c>
-      <c r="F88" t="s">
+      <c r="F88" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
-        <v>6</v>
-      </c>
-      <c r="B89" t="s">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="1">
         <v>38.452390000000001</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="1">
         <v>-121.59285</v>
       </c>
-      <c r="F89" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>6</v>
-      </c>
-      <c r="B90" t="s">
+      <c r="F89" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="1">
         <v>38.063000000000002</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="1">
         <v>-121.80696</v>
       </c>
-      <c r="F90" t="s">
+      <c r="F90" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>6</v>
-      </c>
-      <c r="B91" t="s">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="1">
         <v>38.208170000000003</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="1">
         <v>-122.03394</v>
       </c>
-      <c r="F91" t="s">
+      <c r="F91" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
-        <v>6</v>
-      </c>
-      <c r="B92" t="s">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="1">
         <v>38.35765</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="1">
         <v>-121.63684000000001</v>
       </c>
-      <c r="F92" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
-        <v>6</v>
-      </c>
-      <c r="B93" t="s">
+      <c r="F92" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="1">
         <v>38.330509999999997</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="1">
         <v>-121.64879000000001</v>
       </c>
-      <c r="F93" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
-        <v>6</v>
-      </c>
-      <c r="B94" t="s">
+      <c r="F93" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="1">
         <v>38.465710000000001</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="1">
         <v>-121.58771</v>
       </c>
-      <c r="F94" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
-        <v>6</v>
-      </c>
-      <c r="B95" t="s">
+      <c r="F94" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="1">
         <v>38.073500000000003</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="1">
         <v>-121.97254</v>
       </c>
-      <c r="F95" t="s">
+      <c r="F95" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
-        <v>6</v>
-      </c>
-      <c r="B96" t="s">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="1">
         <v>38.123069999999998</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="1">
         <v>-121.90067000000001</v>
       </c>
-      <c r="F96" t="s">
+      <c r="F96" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>6</v>
       </c>
@@ -3478,4623 +3474,4611 @@
       <c r="F97" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G97" s="3" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
-        <v>6</v>
-      </c>
-      <c r="B98" t="s">
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="1">
         <v>38.247390000000003</v>
       </c>
-      <c r="D98">
+      <c r="D98" s="1">
         <v>-121.67606000000001</v>
       </c>
-      <c r="F98" t="s">
+      <c r="F98" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
-        <v>6</v>
-      </c>
-      <c r="B99" t="s">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="1">
         <v>38.374470000000002</v>
       </c>
-      <c r="D99">
+      <c r="D99" s="1">
         <v>-121.62987</v>
       </c>
-      <c r="F99" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
-        <v>6</v>
-      </c>
-      <c r="B100" t="s">
+      <c r="F99" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="1">
         <v>38.315640000000002</v>
       </c>
-      <c r="D100">
+      <c r="D100" s="1">
         <v>-121.651</v>
       </c>
-      <c r="F100" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
-        <v>6</v>
-      </c>
-      <c r="B101" t="s">
+      <c r="F100" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="1">
         <v>38.367159999999998</v>
       </c>
-      <c r="D101">
+      <c r="D101" s="1">
         <v>-121.63356</v>
       </c>
-      <c r="F101" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
-        <v>6</v>
-      </c>
-      <c r="B102" t="s">
+      <c r="F101" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="1">
         <v>38.100180000000002</v>
       </c>
-      <c r="D102">
+      <c r="D102" s="1">
         <v>-122.02812</v>
       </c>
-      <c r="F102" t="s">
+      <c r="F102" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
-        <v>6</v>
-      </c>
-      <c r="B103" t="s">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="1">
         <v>38.161589999999997</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="1">
         <v>-122.04742</v>
       </c>
-      <c r="F103" t="s">
+      <c r="F103" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
-        <v>6</v>
-      </c>
-      <c r="B104" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C104">
+      <c r="C104" s="1">
         <v>38.049120000000002</v>
       </c>
-      <c r="D104">
+      <c r="D104" s="1">
         <v>-121.95945</v>
       </c>
-      <c r="F104" t="s">
+      <c r="F104" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
-        <v>6</v>
-      </c>
-      <c r="B105" t="s">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="1">
         <v>38.063090000000003</v>
       </c>
-      <c r="D105">
+      <c r="D105" s="1">
         <v>-121.80838</v>
       </c>
-      <c r="F105" t="s">
+      <c r="F105" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
-        <v>6</v>
-      </c>
-      <c r="B106" t="s">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="1">
         <v>38.07526</v>
       </c>
-      <c r="D106">
+      <c r="D106" s="1">
         <v>-121.77106999999999</v>
       </c>
-      <c r="F106" t="s">
+      <c r="F106" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
-        <v>6</v>
-      </c>
-      <c r="B107" t="s">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="1">
         <v>38.466050000000003</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="1">
         <v>-121.58710000000001</v>
       </c>
-      <c r="F107" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
-        <v>6</v>
-      </c>
-      <c r="B108" t="s">
+      <c r="F107" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C108">
+      <c r="C108" s="1">
         <v>38.09357</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="1">
         <v>-122.05553</v>
       </c>
-      <c r="F108" t="s">
+      <c r="F108" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
-        <v>6</v>
-      </c>
-      <c r="B109" t="s">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="1">
         <v>38.063510000000001</v>
       </c>
-      <c r="D109">
+      <c r="D109" s="1">
         <v>-122.11063</v>
       </c>
-      <c r="F109" t="s">
+      <c r="F109" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
-        <v>6</v>
-      </c>
-      <c r="B110" t="s">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="1">
         <v>38.070680000000003</v>
       </c>
-      <c r="D110">
+      <c r="D110" s="1">
         <v>-121.83932</v>
       </c>
-      <c r="F110" t="s">
+      <c r="F110" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
-        <v>6</v>
-      </c>
-      <c r="B111" t="s">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C111">
+      <c r="C111" s="1">
         <v>38.456589999999998</v>
       </c>
-      <c r="D111">
+      <c r="D111" s="1">
         <v>-121.59103</v>
       </c>
-      <c r="F111" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B112" t="s">
+      <c r="F111" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C112">
+      <c r="C112" s="1">
         <v>38.383400000000002</v>
       </c>
-      <c r="D112">
+      <c r="D112" s="1">
         <v>-121.62569999999999</v>
       </c>
-      <c r="F112" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
-        <v>6</v>
-      </c>
-      <c r="B113" t="s">
+      <c r="F112" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C113">
+      <c r="C113" s="1">
         <v>38.108600000000003</v>
       </c>
-      <c r="D113">
+      <c r="D113" s="1">
         <v>-122.05795000000001</v>
       </c>
-      <c r="F113" t="s">
+      <c r="F113" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
-        <v>6</v>
-      </c>
-      <c r="B114" t="s">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C114">
+      <c r="C114" s="1">
         <v>38.288069999999998</v>
       </c>
-      <c r="D114">
+      <c r="D114" s="1">
         <v>-121.65853</v>
       </c>
-      <c r="F114" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
-        <v>6</v>
-      </c>
-      <c r="B115" t="s">
+      <c r="F114" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C115">
+      <c r="C115" s="1">
         <v>38.414200000000001</v>
       </c>
-      <c r="D115">
+      <c r="D115" s="1">
         <v>-121.61171</v>
       </c>
-      <c r="F115" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
-        <v>6</v>
-      </c>
-      <c r="B116" t="s">
+      <c r="F115" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C116">
+      <c r="C116" s="1">
         <v>38.252679999999998</v>
       </c>
-      <c r="D116">
+      <c r="D116" s="1">
         <v>-121.66831000000001</v>
       </c>
-      <c r="F116" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
-        <v>6</v>
-      </c>
-      <c r="B117" t="s">
+      <c r="F116" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C117">
+      <c r="C117" s="1">
         <v>38.436630000000001</v>
       </c>
-      <c r="D117">
+      <c r="D117" s="1">
         <v>-121.60033</v>
       </c>
-      <c r="F117" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
-        <v>6</v>
-      </c>
-      <c r="B118" t="s">
+      <c r="F117" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C118">
+      <c r="C118" s="1">
         <v>38.091009999999997</v>
       </c>
-      <c r="D118">
+      <c r="D118" s="1">
         <v>-122.00775</v>
       </c>
-      <c r="F118" t="s">
+      <c r="F118" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A119" t="s">
-        <v>6</v>
-      </c>
-      <c r="B119" t="s">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C119">
+      <c r="C119" s="1">
         <v>38.064839999999997</v>
       </c>
-      <c r="D119">
+      <c r="D119" s="1">
         <v>-122.11123000000001</v>
       </c>
-      <c r="F119" t="s">
+      <c r="F119" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
-        <v>6</v>
-      </c>
-      <c r="B120" t="s">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C120">
+      <c r="C120" s="1">
         <v>38.33193</v>
       </c>
-      <c r="D120">
+      <c r="D120" s="1">
         <v>-121.64839000000001</v>
       </c>
-      <c r="F120" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
-        <v>6</v>
-      </c>
-      <c r="B121" t="s">
+      <c r="F120" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C121">
+      <c r="C121" s="1">
         <v>38.13608</v>
       </c>
-      <c r="D121">
+      <c r="D121" s="1">
         <v>-122.05981</v>
       </c>
-      <c r="F121" t="s">
+      <c r="F121" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
-        <v>6</v>
-      </c>
-      <c r="B122" t="s">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C122">
+      <c r="C122" s="1">
         <v>38.057209999999998</v>
       </c>
-      <c r="D122">
+      <c r="D122" s="1">
         <v>-121.94953</v>
       </c>
-      <c r="F122" t="s">
+      <c r="F122" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
-        <v>6</v>
-      </c>
-      <c r="B123" t="s">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C123">
+      <c r="C123" s="1">
         <v>38.412309999999998</v>
       </c>
-      <c r="D123">
+      <c r="D123" s="1">
         <v>-121.61233</v>
       </c>
-      <c r="F123" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
-        <v>6</v>
-      </c>
-      <c r="B124" t="s">
+      <c r="F123" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C124">
+      <c r="C124" s="1">
         <v>38.131770000000003</v>
       </c>
-      <c r="D124">
+      <c r="D124" s="1">
         <v>-122.08208</v>
       </c>
-      <c r="F124" t="s">
+      <c r="F124" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
-        <v>6</v>
-      </c>
-      <c r="B125" t="s">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C125">
+      <c r="C125" s="1">
         <v>38.052280000000003</v>
       </c>
-      <c r="D125">
+      <c r="D125" s="1">
         <v>-121.96823999999999</v>
       </c>
-      <c r="F125" t="s">
+      <c r="F125" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
-        <v>6</v>
-      </c>
-      <c r="B126" t="s">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C126">
+      <c r="C126" s="1">
         <v>38.413829999999997</v>
       </c>
-      <c r="D126">
+      <c r="D126" s="1">
         <v>-121.61096000000001</v>
       </c>
-      <c r="F126" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A127" t="s">
-        <v>6</v>
-      </c>
-      <c r="B127" t="s">
+      <c r="F126" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C127">
+      <c r="C127" s="1">
         <v>38.411140000000003</v>
       </c>
-      <c r="D127">
+      <c r="D127" s="1">
         <v>-121.61284999999999</v>
       </c>
-      <c r="F127" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
-        <v>6</v>
-      </c>
-      <c r="B128" t="s">
+      <c r="F127" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C128">
+      <c r="C128" s="1">
         <v>38.350409999999997</v>
       </c>
-      <c r="D128">
+      <c r="D128" s="1">
         <v>-121.64091999999999</v>
       </c>
-      <c r="F128" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
-        <v>6</v>
-      </c>
-      <c r="B129" t="s">
+      <c r="F128" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C129">
+      <c r="C129" s="1">
         <v>38.070070000000001</v>
       </c>
-      <c r="D129">
+      <c r="D129" s="1">
         <v>-121.97401000000001</v>
       </c>
-      <c r="F129" t="s">
+      <c r="F129" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
-        <v>6</v>
-      </c>
-      <c r="B130" t="s">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C130">
+      <c r="C130" s="1">
         <v>38.047879999999999</v>
       </c>
-      <c r="D130">
+      <c r="D130" s="1">
         <v>-121.87357</v>
       </c>
-      <c r="F130" t="s">
+      <c r="F130" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
-        <v>6</v>
-      </c>
-      <c r="B131" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C131">
+      <c r="C131" s="1">
         <v>38.065179999999998</v>
       </c>
-      <c r="D131">
+      <c r="D131" s="1">
         <v>-121.81926</v>
       </c>
-      <c r="F131" t="s">
+      <c r="F131" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
-        <v>6</v>
-      </c>
-      <c r="B132" t="s">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C132">
+      <c r="C132" s="1">
         <v>38.353520000000003</v>
       </c>
-      <c r="D132">
+      <c r="D132" s="1">
         <v>-121.63890000000001</v>
       </c>
-      <c r="F132" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A133" t="s">
-        <v>6</v>
-      </c>
-      <c r="B133" t="s">
+      <c r="F132" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C133">
+      <c r="C133" s="1">
         <v>38.049720000000001</v>
       </c>
-      <c r="D133">
+      <c r="D133" s="1">
         <v>-121.93016</v>
       </c>
-      <c r="F133" t="s">
+      <c r="F133" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
-        <v>6</v>
-      </c>
-      <c r="B134" t="s">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C134">
+      <c r="C134" s="1">
         <v>38.061599999999999</v>
       </c>
-      <c r="D134">
+      <c r="D134" s="1">
         <v>-121.95479</v>
       </c>
-      <c r="F134" t="s">
+      <c r="F134" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
-        <v>6</v>
-      </c>
-      <c r="B135" t="s">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C135">
+      <c r="C135" s="1">
         <v>38.06597</v>
       </c>
-      <c r="D135">
+      <c r="D135" s="1">
         <v>-121.81925</v>
       </c>
-      <c r="F135" t="s">
+      <c r="F135" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
-        <v>6</v>
-      </c>
-      <c r="B136" t="s">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C136">
+      <c r="C136" s="1">
         <v>38.430349999999997</v>
       </c>
-      <c r="D136">
+      <c r="D136" s="1">
         <v>-121.60382</v>
       </c>
-      <c r="F136" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
-        <v>6</v>
-      </c>
-      <c r="B137" t="s">
+      <c r="F136" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C137">
+      <c r="C137" s="1">
         <v>38.532249999999998</v>
       </c>
-      <c r="D137">
+      <c r="D137" s="1">
         <v>-121.58405</v>
       </c>
-      <c r="F137" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
-        <v>6</v>
-      </c>
-      <c r="B138" t="s">
+      <c r="F137" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C138">
+      <c r="C138" s="1">
         <v>38.552289999999999</v>
       </c>
-      <c r="D138">
+      <c r="D138" s="1">
         <v>-121.57859999999999</v>
       </c>
-      <c r="F138" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
-        <v>6</v>
-      </c>
-      <c r="B139" t="s">
+      <c r="F138" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C139">
+      <c r="C139" s="1">
         <v>38.375109999999999</v>
       </c>
-      <c r="D139">
+      <c r="D139" s="1">
         <v>-121.62864</v>
       </c>
-      <c r="F139" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
-        <v>6</v>
-      </c>
-      <c r="B140" t="s">
+      <c r="F139" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C140">
+      <c r="C140" s="1">
         <v>38.482909999999997</v>
       </c>
-      <c r="D140">
+      <c r="D140" s="1">
         <v>-121.58450999999999</v>
       </c>
-      <c r="F140" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
-        <v>6</v>
-      </c>
-      <c r="B141" t="s">
+      <c r="F140" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C141">
+      <c r="C141" s="1">
         <v>38.417119999999997</v>
       </c>
-      <c r="D141">
+      <c r="D141" s="1">
         <v>-121.60992</v>
       </c>
-      <c r="F141" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
-        <v>6</v>
-      </c>
-      <c r="B142" t="s">
+      <c r="F141" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C142">
+      <c r="C142" s="1">
         <v>38.43206</v>
       </c>
-      <c r="D142">
+      <c r="D142" s="1">
         <v>-121.60307</v>
       </c>
-      <c r="F142" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
-        <v>6</v>
-      </c>
-      <c r="B143" t="s">
+      <c r="F142" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C143">
+      <c r="C143" s="1">
         <v>38.319380000000002</v>
       </c>
-      <c r="D143">
+      <c r="D143" s="1">
         <v>-121.65044</v>
       </c>
-      <c r="F143" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
-        <v>6</v>
-      </c>
-      <c r="B144" t="s">
+      <c r="F143" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C144">
+      <c r="C144" s="1">
         <v>38.3583</v>
       </c>
-      <c r="D144">
+      <c r="D144" s="1">
         <v>-121.63628</v>
       </c>
-      <c r="F144" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
-        <v>6</v>
-      </c>
-      <c r="B145" t="s">
+      <c r="F144" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C145">
+      <c r="C145" s="1">
         <v>38.334299999999999</v>
       </c>
-      <c r="D145">
+      <c r="D145" s="1">
         <v>-121.64700000000001</v>
       </c>
-      <c r="F145" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
-        <v>6</v>
-      </c>
-      <c r="B146" t="s">
+      <c r="F145" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C146">
+      <c r="C146" s="1">
         <v>38.406329999999997</v>
       </c>
-      <c r="D146">
+      <c r="D146" s="1">
         <v>-121.61521</v>
       </c>
-      <c r="F146" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
-        <v>6</v>
-      </c>
-      <c r="B147" t="s">
+      <c r="F146" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C147">
+      <c r="C147" s="1">
         <v>38.361609999999999</v>
       </c>
-      <c r="D147">
+      <c r="D147" s="1">
         <v>-121.63608000000001</v>
       </c>
-      <c r="F147" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
-        <v>6</v>
-      </c>
-      <c r="B148" t="s">
+      <c r="F147" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C148">
+      <c r="C148" s="1">
         <v>38.141979999999997</v>
       </c>
-      <c r="D148">
+      <c r="D148" s="1">
         <v>-122.06095000000001</v>
       </c>
-      <c r="F148" t="s">
+      <c r="F148" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
-        <v>6</v>
-      </c>
-      <c r="B149" t="s">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C149">
+      <c r="C149" s="1">
         <v>38.070810000000002</v>
       </c>
-      <c r="D149">
+      <c r="D149" s="1">
         <v>-121.84148999999999</v>
       </c>
-      <c r="F149" t="s">
+      <c r="F149" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
-        <v>6</v>
-      </c>
-      <c r="B150" t="s">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C150">
+      <c r="C150" s="1">
         <v>38.335680000000004</v>
       </c>
-      <c r="D150">
+      <c r="D150" s="1">
         <v>-121.64635</v>
       </c>
-      <c r="F150" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A151" t="s">
-        <v>6</v>
-      </c>
-      <c r="B151" t="s">
+      <c r="F150" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C151">
+      <c r="C151" s="1">
         <v>38.087760000000003</v>
       </c>
-      <c r="D151">
+      <c r="D151" s="1">
         <v>-121.74742999999999</v>
       </c>
-      <c r="F151" t="s">
+      <c r="F151" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A152" t="s">
-        <v>6</v>
-      </c>
-      <c r="B152" t="s">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C152">
+      <c r="C152" s="1">
         <v>38.287739999999999</v>
       </c>
-      <c r="D152">
+      <c r="D152" s="1">
         <v>-121.65816</v>
       </c>
-      <c r="F152" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A153" t="s">
-        <v>6</v>
-      </c>
-      <c r="B153" t="s">
+      <c r="F152" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C153">
+      <c r="C153" s="1">
         <v>38.361159999999998</v>
       </c>
-      <c r="D153">
+      <c r="D153" s="1">
         <v>-121.6357</v>
       </c>
-      <c r="F153" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A154" t="s">
-        <v>6</v>
-      </c>
-      <c r="B154" t="s">
+      <c r="F153" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C154">
+      <c r="C154" s="1">
         <v>38.352060000000002</v>
       </c>
-      <c r="D154">
+      <c r="D154" s="1">
         <v>-121.63934999999999</v>
       </c>
-      <c r="F154" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A155" t="s">
-        <v>6</v>
-      </c>
-      <c r="B155" t="s">
+      <c r="F154" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C155">
+      <c r="C155" s="1">
         <v>38.103549999999998</v>
       </c>
-      <c r="D155">
+      <c r="D155" s="1">
         <v>-121.72169</v>
       </c>
-      <c r="F155" t="s">
+      <c r="F155" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A156" t="s">
-        <v>6</v>
-      </c>
-      <c r="B156" t="s">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C156">
+      <c r="C156" s="1">
         <v>38.421720000000001</v>
       </c>
-      <c r="D156">
+      <c r="D156" s="1">
         <v>-121.60709</v>
       </c>
-      <c r="F156" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A157" t="s">
-        <v>6</v>
-      </c>
-      <c r="B157" t="s">
+      <c r="F156" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C157">
+      <c r="C157" s="1">
         <v>38.107100000000003</v>
       </c>
-      <c r="D157">
+      <c r="D157" s="1">
         <v>-122.05146000000001</v>
       </c>
-      <c r="F157" t="s">
+      <c r="F157" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A158" t="s">
-        <v>6</v>
-      </c>
-      <c r="B158" t="s">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C158">
+      <c r="C158" s="1">
         <v>38.069040000000001</v>
       </c>
-      <c r="D158">
+      <c r="D158" s="1">
         <v>-121.78211</v>
       </c>
-      <c r="F158" t="s">
+      <c r="F158" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A159" t="s">
-        <v>6</v>
-      </c>
-      <c r="B159" t="s">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C159">
+      <c r="C159" s="1">
         <v>38.317749999999997</v>
       </c>
-      <c r="D159">
+      <c r="D159" s="1">
         <v>-121.65138</v>
       </c>
-      <c r="F159" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A160" t="s">
-        <v>6</v>
-      </c>
-      <c r="B160" t="s">
+      <c r="F159" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C160">
+      <c r="C160" s="1">
         <v>38.106520000000003</v>
       </c>
-      <c r="D160">
+      <c r="D160" s="1">
         <v>-122.04843</v>
       </c>
-      <c r="F160" t="s">
+      <c r="F160" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A161" t="s">
-        <v>6</v>
-      </c>
-      <c r="B161" t="s">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C161">
+      <c r="C161" s="1">
         <v>38.393729999999998</v>
       </c>
-      <c r="D161">
+      <c r="D161" s="1">
         <v>-121.62087</v>
       </c>
-      <c r="F161" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A162" t="s">
-        <v>6</v>
-      </c>
-      <c r="B162" t="s">
+      <c r="F161" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C162">
+      <c r="C162" s="1">
         <v>38.307429999999997</v>
       </c>
-      <c r="D162">
+      <c r="D162" s="1">
         <v>-121.65391</v>
       </c>
-      <c r="F162" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A163" t="s">
-        <v>6</v>
-      </c>
-      <c r="B163" t="s">
+      <c r="F162" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C163">
+      <c r="C163" s="1">
         <v>38.166800000000002</v>
       </c>
-      <c r="D163">
+      <c r="D163" s="1">
         <v>-122.04379</v>
       </c>
-      <c r="F163" t="s">
+      <c r="F163" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A164" t="s">
-        <v>6</v>
-      </c>
-      <c r="B164" t="s">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C164">
+      <c r="C164" s="1">
         <v>38.17839</v>
       </c>
-      <c r="D164">
+      <c r="D164" s="1">
         <v>-122.05043999999999</v>
       </c>
-      <c r="F164" t="s">
+      <c r="F164" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A165" t="s">
-        <v>6</v>
-      </c>
-      <c r="B165" t="s">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C165">
+      <c r="C165" s="1">
         <v>38.449170000000002</v>
       </c>
-      <c r="D165">
+      <c r="D165" s="1">
         <v>-121.59496</v>
       </c>
-      <c r="F165" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A166" t="s">
-        <v>6</v>
-      </c>
-      <c r="B166" t="s">
+      <c r="F165" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C166">
+      <c r="C166" s="1">
         <v>38.450629999999997</v>
       </c>
-      <c r="D166">
+      <c r="D166" s="1">
         <v>-121.59487</v>
       </c>
-      <c r="F166" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A167" t="s">
-        <v>6</v>
-      </c>
-      <c r="B167" t="s">
+      <c r="F166" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C167">
+      <c r="C167" s="1">
         <v>38.286520000000003</v>
       </c>
-      <c r="D167">
+      <c r="D167" s="1">
         <v>-121.65895</v>
       </c>
-      <c r="F167" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A168" t="s">
-        <v>6</v>
-      </c>
-      <c r="B168" t="s">
+      <c r="F167" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C168">
+      <c r="C168" s="1">
         <v>38.075279999999999</v>
       </c>
-      <c r="D168">
+      <c r="D168" s="1">
         <v>-121.76174</v>
       </c>
-      <c r="F168" t="s">
+      <c r="F168" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A169" t="s">
-        <v>6</v>
-      </c>
-      <c r="B169" t="s">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C169">
+      <c r="C169" s="1">
         <v>38.139589999999998</v>
       </c>
-      <c r="D169">
+      <c r="D169" s="1">
         <v>-121.69361000000001</v>
       </c>
-      <c r="F169" t="s">
+      <c r="F169" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A170" t="s">
-        <v>6</v>
-      </c>
-      <c r="B170" t="s">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C170">
+      <c r="C170" s="1">
         <v>38.152270000000001</v>
       </c>
-      <c r="D170">
+      <c r="D170" s="1">
         <v>-121.68227</v>
       </c>
-      <c r="F170" t="s">
+      <c r="F170" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A171" t="s">
-        <v>6</v>
-      </c>
-      <c r="B171" t="s">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C171">
+      <c r="C171" s="1">
         <v>38.091149999999999</v>
       </c>
-      <c r="D171">
+      <c r="D171" s="1">
         <v>-121.57612</v>
       </c>
-      <c r="F171" t="s">
+      <c r="F171" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A172" t="s">
-        <v>6</v>
-      </c>
-      <c r="B172" t="s">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C172">
+      <c r="C172" s="1">
         <v>38.104689999999998</v>
       </c>
-      <c r="D172">
+      <c r="D172" s="1">
         <v>-121.69494</v>
       </c>
-      <c r="F172" t="s">
+      <c r="F172" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A173" t="s">
-        <v>6</v>
-      </c>
-      <c r="B173" t="s">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C173">
+      <c r="C173" s="1">
         <v>38.562519999999999</v>
       </c>
-      <c r="D173">
+      <c r="D173" s="1">
         <v>-121.55421</v>
       </c>
-      <c r="F173" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A174" t="s">
-        <v>6</v>
-      </c>
-      <c r="B174" t="s">
+      <c r="F173" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C174">
+      <c r="C174" s="1">
         <v>38.064410000000002</v>
       </c>
-      <c r="D174">
+      <c r="D174" s="1">
         <v>-121.78788</v>
       </c>
-      <c r="F174" t="s">
+      <c r="F174" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A175" t="s">
-        <v>6</v>
-      </c>
-      <c r="B175" t="s">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C175">
+      <c r="C175" s="1">
         <v>38.119880000000002</v>
       </c>
-      <c r="D175">
+      <c r="D175" s="1">
         <v>-121.69616000000001</v>
       </c>
-      <c r="F175" t="s">
+      <c r="F175" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A176" t="s">
-        <v>6</v>
-      </c>
-      <c r="B176" t="s">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C176">
+      <c r="C176" s="1">
         <v>38.1477</v>
       </c>
-      <c r="D176">
+      <c r="D176" s="1">
         <v>-121.6841</v>
       </c>
-      <c r="F176" t="s">
+      <c r="F176" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A177" t="s">
-        <v>6</v>
-      </c>
-      <c r="B177" t="s">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C177">
+      <c r="C177" s="1">
         <v>38.093060000000001</v>
       </c>
-      <c r="D177">
+      <c r="D177" s="1">
         <v>-121.73622</v>
       </c>
-      <c r="F177" t="s">
+      <c r="F177" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A178" t="s">
-        <v>6</v>
-      </c>
-      <c r="B178" t="s">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C178">
+      <c r="C178" s="1">
         <v>38.274630000000002</v>
       </c>
-      <c r="D178">
+      <c r="D178" s="1">
         <v>-121.66211</v>
       </c>
-      <c r="F178" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A179" t="s">
-        <v>6</v>
-      </c>
-      <c r="B179" t="s">
+      <c r="F178" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C179">
+      <c r="C179" s="1">
         <v>38.17371</v>
       </c>
-      <c r="D179">
+      <c r="D179" s="1">
         <v>-121.94799</v>
       </c>
-      <c r="F179" t="s">
+      <c r="F179" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A180" t="s">
-        <v>6</v>
-      </c>
-      <c r="B180" t="s">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C180">
+      <c r="C180" s="1">
         <v>38.075099999999999</v>
       </c>
-      <c r="D180">
+      <c r="D180" s="1">
         <v>-121.76117000000001</v>
       </c>
-      <c r="F180" t="s">
+      <c r="F180" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A181" t="s">
-        <v>6</v>
-      </c>
-      <c r="B181" t="s">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C181">
+      <c r="C181" s="1">
         <v>38.029229999999998</v>
       </c>
-      <c r="D181">
+      <c r="D181" s="1">
         <v>-121.74611</v>
       </c>
-      <c r="F181" t="s">
+      <c r="F181" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A182" t="s">
-        <v>6</v>
-      </c>
-      <c r="B182" t="s">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C182">
+      <c r="C182" s="1">
         <v>38.418590000000002</v>
       </c>
-      <c r="D182">
+      <c r="D182" s="1">
         <v>-121.60923</v>
       </c>
-      <c r="F182" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A183" t="s">
-        <v>6</v>
-      </c>
-      <c r="B183" t="s">
+      <c r="F182" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C183">
+      <c r="C183" s="1">
         <v>38.081049999999998</v>
       </c>
-      <c r="D183">
+      <c r="D183" s="1">
         <v>-121.75703</v>
       </c>
-      <c r="F183" t="s">
+      <c r="F183" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A184" t="s">
-        <v>6</v>
-      </c>
-      <c r="B184" t="s">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C184">
+      <c r="C184" s="1">
         <v>38.1873</v>
       </c>
-      <c r="D184">
+      <c r="D184" s="1">
         <v>-121.97494</v>
       </c>
-      <c r="F184" t="s">
+      <c r="F184" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A185" t="s">
-        <v>6</v>
-      </c>
-      <c r="B185" t="s">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C185">
+      <c r="C185" s="1">
         <v>38.343209999999999</v>
       </c>
-      <c r="D185">
+      <c r="D185" s="1">
         <v>-121.6443</v>
       </c>
-      <c r="F185" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A186" t="s">
-        <v>6</v>
-      </c>
-      <c r="B186" t="s">
+      <c r="F185" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C186">
+      <c r="C186" s="1">
         <v>38.185630000000003</v>
       </c>
-      <c r="D186">
+      <c r="D186" s="1">
         <v>-121.92966</v>
       </c>
-      <c r="F186" t="s">
+      <c r="F186" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A187" t="s">
-        <v>6</v>
-      </c>
-      <c r="B187" t="s">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C187">
+      <c r="C187" s="1">
         <v>38.388019999999997</v>
       </c>
-      <c r="D187">
+      <c r="D187" s="1">
         <v>-121.62251999999999</v>
       </c>
-      <c r="F187" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A188" t="s">
-        <v>6</v>
-      </c>
-      <c r="B188" t="s">
+      <c r="F187" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C188">
+      <c r="C188" s="1">
         <v>38.42353</v>
       </c>
-      <c r="D188">
+      <c r="D188" s="1">
         <v>-121.60612</v>
       </c>
-      <c r="F188" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A189" t="s">
-        <v>6</v>
-      </c>
-      <c r="B189" t="s">
+      <c r="F188" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C189">
+      <c r="C189" s="1">
         <v>38.195860000000003</v>
       </c>
-      <c r="D189">
+      <c r="D189" s="1">
         <v>-122.04409</v>
       </c>
-      <c r="F189" t="s">
+      <c r="F189" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A190" t="s">
-        <v>6</v>
-      </c>
-      <c r="B190" t="s">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C190">
+      <c r="C190" s="1">
         <v>38.489899999999999</v>
       </c>
-      <c r="D190">
+      <c r="D190" s="1">
         <v>-121.58387</v>
       </c>
-      <c r="F190" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A191" t="s">
-        <v>6</v>
-      </c>
-      <c r="B191" t="s">
+      <c r="F190" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C191">
+      <c r="C191" s="1">
         <v>38.360309999999998</v>
       </c>
-      <c r="D191">
+      <c r="D191" s="1">
         <v>-121.63593</v>
       </c>
-      <c r="F191" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A192" t="s">
-        <v>6</v>
-      </c>
-      <c r="B192" t="s">
+      <c r="F191" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="C192">
+      <c r="C192" s="1">
         <v>38.174349999999997</v>
       </c>
-      <c r="D192">
+      <c r="D192" s="1">
         <v>-121.94875999999999</v>
       </c>
-      <c r="F192" t="s">
+      <c r="F192" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A193" t="s">
-        <v>6</v>
-      </c>
-      <c r="B193" t="s">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C193">
+      <c r="C193" s="1">
         <v>38.180439999999997</v>
       </c>
-      <c r="D193">
+      <c r="D193" s="1">
         <v>-121.99449</v>
       </c>
-      <c r="F193" t="s">
+      <c r="F193" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A194" t="s">
-        <v>6</v>
-      </c>
-      <c r="B194" t="s">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A194" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C194">
+      <c r="C194" s="1">
         <v>38.40643</v>
       </c>
-      <c r="D194">
+      <c r="D194" s="1">
         <v>-121.61509</v>
       </c>
-      <c r="F194" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A195" t="s">
-        <v>6</v>
-      </c>
-      <c r="B195" t="s">
+      <c r="F194" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="C195">
+      <c r="C195" s="1">
         <v>38.374690000000001</v>
       </c>
-      <c r="D195">
+      <c r="D195" s="1">
         <v>-121.63328</v>
       </c>
-      <c r="F195" t="s">
+      <c r="F195" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A196" t="s">
-        <v>6</v>
-      </c>
-      <c r="B196" t="s">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C196">
+      <c r="C196" s="1">
         <v>38.45438</v>
       </c>
-      <c r="D196">
+      <c r="D196" s="1">
         <v>-121.59321</v>
       </c>
-      <c r="F196" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A197" t="s">
-        <v>6</v>
-      </c>
-      <c r="B197" t="s">
+      <c r="F196" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C197">
+      <c r="C197" s="1">
         <v>38.411749999999998</v>
       </c>
-      <c r="D197">
+      <c r="D197" s="1">
         <v>-121.61150000000001</v>
       </c>
-      <c r="F197" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A198" t="s">
-        <v>6</v>
-      </c>
-      <c r="B198" t="s">
+      <c r="F197" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C198">
+      <c r="C198" s="1">
         <v>38.174750000000003</v>
       </c>
-      <c r="D198">
+      <c r="D198" s="1">
         <v>-121.96321</v>
       </c>
-      <c r="F198" t="s">
+      <c r="F198" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A199" t="s">
-        <v>6</v>
-      </c>
-      <c r="B199" t="s">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C199">
+      <c r="C199" s="1">
         <v>38.494720000000001</v>
       </c>
-      <c r="D199">
+      <c r="D199" s="1">
         <v>-121.58368</v>
       </c>
-      <c r="F199" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A200" t="s">
-        <v>6</v>
-      </c>
-      <c r="B200" t="s">
+      <c r="F199" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C200">
+      <c r="C200" s="1">
         <v>38.436309999999999</v>
       </c>
-      <c r="D200">
+      <c r="D200" s="1">
         <v>-121.60037</v>
       </c>
-      <c r="F200" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A201" t="s">
-        <v>6</v>
-      </c>
-      <c r="B201" t="s">
+      <c r="F200" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C201">
+      <c r="C201" s="1">
         <v>38.187100000000001</v>
       </c>
-      <c r="D201">
+      <c r="D201" s="1">
         <v>-121.97976</v>
       </c>
-      <c r="F201" t="s">
+      <c r="F201" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A202" t="s">
-        <v>6</v>
-      </c>
-      <c r="B202" t="s">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C202">
+      <c r="C202" s="1">
         <v>38.050719999999998</v>
       </c>
-      <c r="D202">
+      <c r="D202" s="1">
         <v>-121.89534</v>
       </c>
-      <c r="F202" t="s">
+      <c r="F202" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A203" t="s">
-        <v>6</v>
-      </c>
-      <c r="B203" t="s">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C203">
+      <c r="C203" s="1">
         <v>38.104230000000001</v>
       </c>
-      <c r="D203">
+      <c r="D203" s="1">
         <v>-121.70987</v>
       </c>
-      <c r="F203" t="s">
+      <c r="F203" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A204" t="s">
-        <v>6</v>
-      </c>
-      <c r="B204" t="s">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A204" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C204">
+      <c r="C204" s="1">
         <v>38.180799999999998</v>
       </c>
-      <c r="D204">
+      <c r="D204" s="1">
         <v>-121.99506</v>
       </c>
-      <c r="F204" t="s">
+      <c r="F204" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A205" t="s">
-        <v>6</v>
-      </c>
-      <c r="B205" t="s">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A205" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C205">
+      <c r="C205" s="1">
         <v>38.50132</v>
       </c>
-      <c r="D205">
+      <c r="D205" s="1">
         <v>-121.58463999999999</v>
       </c>
-      <c r="F205" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A206" t="s">
-        <v>6</v>
-      </c>
-      <c r="B206" t="s">
+      <c r="F205" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="C206">
+      <c r="C206" s="1">
         <v>38.444000000000003</v>
       </c>
-      <c r="D206">
+      <c r="D206" s="1">
         <v>-121.59748</v>
       </c>
-      <c r="F206" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A207" t="s">
-        <v>6</v>
-      </c>
-      <c r="B207" t="s">
+      <c r="F206" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="C207">
+      <c r="C207" s="1">
         <v>38.41254</v>
       </c>
-      <c r="D207">
+      <c r="D207" s="1">
         <v>-121.61125</v>
       </c>
-      <c r="F207" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A208" t="s">
-        <v>6</v>
-      </c>
-      <c r="B208" t="s">
+      <c r="F207" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C208">
+      <c r="C208" s="1">
         <v>38.408270000000002</v>
       </c>
-      <c r="D208">
+      <c r="D208" s="1">
         <v>-121.61375</v>
       </c>
-      <c r="F208" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A209" t="s">
-        <v>6</v>
-      </c>
-      <c r="B209" t="s">
+      <c r="F208" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C209">
+      <c r="C209" s="1">
         <v>38.330660000000002</v>
       </c>
-      <c r="D209">
+      <c r="D209" s="1">
         <v>-121.64878</v>
       </c>
-      <c r="F209" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A210" t="s">
-        <v>6</v>
-      </c>
-      <c r="B210" t="s">
+      <c r="F209" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C210">
+      <c r="C210" s="1">
         <v>38.077449999999999</v>
       </c>
-      <c r="D210">
+      <c r="D210" s="1">
         <v>-121.76734999999999</v>
       </c>
-      <c r="F210" t="s">
+      <c r="F210" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A211" t="s">
-        <v>6</v>
-      </c>
-      <c r="B211" t="s">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="C211">
+      <c r="C211" s="1">
         <v>38.084200000000003</v>
       </c>
-      <c r="D211">
+      <c r="D211" s="1">
         <v>-121.75209</v>
       </c>
-      <c r="F211" t="s">
+      <c r="F211" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A212" t="s">
-        <v>6</v>
-      </c>
-      <c r="B212" t="s">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="C212">
+      <c r="C212" s="1">
         <v>38.064999999999998</v>
       </c>
-      <c r="D212">
+      <c r="D212" s="1">
         <v>-121.81516000000001</v>
       </c>
-      <c r="F212" t="s">
+      <c r="F212" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A213" t="s">
-        <v>6</v>
-      </c>
-      <c r="B213" t="s">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="C213">
+      <c r="C213" s="1">
         <v>38.406179999999999</v>
       </c>
-      <c r="D213">
+      <c r="D213" s="1">
         <v>-121.61519</v>
       </c>
-      <c r="F213" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A214" t="s">
-        <v>6</v>
-      </c>
-      <c r="B214" t="s">
+      <c r="F213" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C214">
+      <c r="C214" s="1">
         <v>38.416429999999998</v>
       </c>
-      <c r="D214">
+      <c r="D214" s="1">
         <v>-121.61046</v>
       </c>
-      <c r="F214" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A215" t="s">
-        <v>6</v>
-      </c>
-      <c r="B215" t="s">
+      <c r="F214" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C215">
+      <c r="C215" s="1">
         <v>38.11065</v>
       </c>
-      <c r="D215">
+      <c r="D215" s="1">
         <v>-122.05618</v>
       </c>
-      <c r="F215" t="s">
+      <c r="F215" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A216" t="s">
-        <v>6</v>
-      </c>
-      <c r="B216" t="s">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C216">
+      <c r="C216" s="1">
         <v>38.076169999999998</v>
       </c>
-      <c r="D216">
+      <c r="D216" s="1">
         <v>-121.76103999999999</v>
       </c>
-      <c r="F216" t="s">
+      <c r="F216" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A217" t="s">
-        <v>6</v>
-      </c>
-      <c r="B217" t="s">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C217">
+      <c r="C217" s="1">
         <v>38.080840000000002</v>
       </c>
-      <c r="D217">
+      <c r="D217" s="1">
         <v>-121.76024</v>
       </c>
-      <c r="F217" t="s">
+      <c r="F217" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A218" t="s">
-        <v>6</v>
-      </c>
-      <c r="B218" t="s">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="C218">
+      <c r="C218" s="1">
         <v>38.019210000000001</v>
       </c>
-      <c r="D218">
+      <c r="D218" s="1">
         <v>-121.6074</v>
       </c>
-      <c r="F218" t="s">
+      <c r="F218" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A219" t="s">
-        <v>6</v>
-      </c>
-      <c r="B219" t="s">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C219">
+      <c r="C219" s="1">
         <v>38.244070000000001</v>
       </c>
-      <c r="D219">
+      <c r="D219" s="1">
         <v>-121.68277999999999</v>
       </c>
-      <c r="F219" t="s">
+      <c r="F219" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A220" t="s">
-        <v>6</v>
-      </c>
-      <c r="B220" t="s">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C220">
+      <c r="C220" s="1">
         <v>38.104199999999999</v>
       </c>
-      <c r="D220">
+      <c r="D220" s="1">
         <v>-121.69783</v>
       </c>
-      <c r="F220" t="s">
+      <c r="F220" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A221" t="s">
-        <v>6</v>
-      </c>
-      <c r="B221" t="s">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="C221">
+      <c r="C221" s="1">
         <v>38.09431</v>
       </c>
-      <c r="D221">
+      <c r="D221" s="1">
         <v>-122.06007</v>
       </c>
-      <c r="F221" t="s">
+      <c r="F221" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A222" t="s">
-        <v>6</v>
-      </c>
-      <c r="B222" t="s">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="C222">
+      <c r="C222" s="1">
         <v>38.243639999999999</v>
       </c>
-      <c r="D222">
+      <c r="D222" s="1">
         <v>-121.6863</v>
       </c>
-      <c r="F222" t="s">
+      <c r="F222" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A223" t="s">
-        <v>6</v>
-      </c>
-      <c r="B223" t="s">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C223">
+      <c r="C223" s="1">
         <v>38.02073</v>
       </c>
-      <c r="D223">
+      <c r="D223" s="1">
         <v>-121.80663</v>
       </c>
-      <c r="F223" t="s">
+      <c r="F223" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A224" t="s">
-        <v>6</v>
-      </c>
-      <c r="B224" t="s">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C224">
+      <c r="C224" s="1">
         <v>38.1021</v>
       </c>
-      <c r="D224">
+      <c r="D224" s="1">
         <v>-121.71881</v>
       </c>
-      <c r="F224" t="s">
+      <c r="F224" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A225" t="s">
-        <v>6</v>
-      </c>
-      <c r="B225" t="s">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C225">
+      <c r="C225" s="1">
         <v>38.085169999999998</v>
       </c>
-      <c r="D225">
+      <c r="D225" s="1">
         <v>-121.75193</v>
       </c>
-      <c r="F225" t="s">
+      <c r="F225" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A226" t="s">
-        <v>6</v>
-      </c>
-      <c r="B226" t="s">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C226">
+      <c r="C226" s="1">
         <v>38.088549999999998</v>
       </c>
-      <c r="D226">
+      <c r="D226" s="1">
         <v>-121.7443</v>
       </c>
-      <c r="F226" t="s">
+      <c r="F226" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A227" t="s">
-        <v>6</v>
-      </c>
-      <c r="B227" t="s">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C227">
+      <c r="C227" s="1">
         <v>38.050170000000001</v>
       </c>
-      <c r="D227">
+      <c r="D227" s="1">
         <v>-122.08053</v>
       </c>
-      <c r="F227" t="s">
+      <c r="F227" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A228" t="s">
-        <v>6</v>
-      </c>
-      <c r="B228" t="s">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="C228">
+      <c r="C228" s="1">
         <v>38.098329999999997</v>
       </c>
-      <c r="D228">
+      <c r="D228" s="1">
         <v>-122.05342</v>
       </c>
-      <c r="F228" t="s">
+      <c r="F228" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A229" t="s">
-        <v>6</v>
-      </c>
-      <c r="B229" t="s">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C229">
+      <c r="C229" s="1">
         <v>38.38391</v>
       </c>
-      <c r="D229">
+      <c r="D229" s="1">
         <v>-121.62517</v>
       </c>
-      <c r="F229" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A230" t="s">
-        <v>6</v>
-      </c>
-      <c r="B230" t="s">
+      <c r="F229" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C230">
+      <c r="C230" s="1">
         <v>38.310450000000003</v>
       </c>
-      <c r="D230">
+      <c r="D230" s="1">
         <v>-121.65272</v>
       </c>
-      <c r="F230" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A231" t="s">
-        <v>6</v>
-      </c>
-      <c r="B231" t="s">
+      <c r="F230" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C231">
+      <c r="C231" s="1">
         <v>38.290300000000002</v>
       </c>
-      <c r="D231">
+      <c r="D231" s="1">
         <v>-121.69320999999999</v>
       </c>
-      <c r="F231" t="s">
+      <c r="F231" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A232" t="s">
-        <v>6</v>
-      </c>
-      <c r="B232" t="s">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C232">
+      <c r="C232" s="1">
         <v>38.12088</v>
       </c>
-      <c r="D232">
+      <c r="D232" s="1">
         <v>-121.70392</v>
       </c>
-      <c r="F232" t="s">
+      <c r="F232" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A233" t="s">
-        <v>6</v>
-      </c>
-      <c r="B233" t="s">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C233">
+      <c r="C233" s="1">
         <v>38.327199999999998</v>
       </c>
-      <c r="D233">
+      <c r="D233" s="1">
         <v>-121.64854</v>
       </c>
-      <c r="F233" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A234" t="s">
-        <v>6</v>
-      </c>
-      <c r="B234" t="s">
+      <c r="F233" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="C234">
+      <c r="C234" s="1">
         <v>38.131430000000002</v>
       </c>
-      <c r="D234">
+      <c r="D234" s="1">
         <v>-121.69662</v>
       </c>
-      <c r="F234" t="s">
+      <c r="F234" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A235" t="s">
-        <v>6</v>
-      </c>
-      <c r="B235" t="s">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="C235">
+      <c r="C235" s="1">
         <v>38.131050000000002</v>
       </c>
-      <c r="D235">
+      <c r="D235" s="1">
         <v>-121.91543</v>
       </c>
-      <c r="F235" t="s">
+      <c r="F235" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A236" t="s">
-        <v>6</v>
-      </c>
-      <c r="B236" t="s">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B236" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C236">
+      <c r="C236" s="1">
         <v>38.245060000000002</v>
       </c>
-      <c r="D236">
+      <c r="D236" s="1">
         <v>-121.67077999999999</v>
       </c>
-      <c r="F236" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A237" t="s">
-        <v>6</v>
-      </c>
-      <c r="B237" t="s">
+      <c r="F236" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B237" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="C237">
+      <c r="C237" s="1">
         <v>38.334580000000003</v>
       </c>
-      <c r="D237">
+      <c r="D237" s="1">
         <v>-121.64671</v>
       </c>
-      <c r="F237" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A238" t="s">
-        <v>6</v>
-      </c>
-      <c r="B238" t="s">
+      <c r="F237" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A238" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B238" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C238">
+      <c r="C238" s="1">
         <v>38.041550000000001</v>
       </c>
-      <c r="D238">
+      <c r="D238" s="1">
         <v>-121.84124</v>
       </c>
-      <c r="F238" t="s">
+      <c r="F238" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A239" t="s">
-        <v>6</v>
-      </c>
-      <c r="B239" t="s">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B239" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C239">
+      <c r="C239" s="1">
         <v>38.104770000000002</v>
       </c>
-      <c r="D239">
+      <c r="D239" s="1">
         <v>-122.04037</v>
       </c>
-      <c r="F239" t="s">
+      <c r="F239" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A240" t="s">
-        <v>6</v>
-      </c>
-      <c r="B240" t="s">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A240" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B240" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C240">
+      <c r="C240" s="1">
         <v>38.080710000000003</v>
       </c>
-      <c r="D240">
+      <c r="D240" s="1">
         <v>-122.06121</v>
       </c>
-      <c r="F240" t="s">
+      <c r="F240" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A241" t="s">
-        <v>6</v>
-      </c>
-      <c r="B241" t="s">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B241" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C241">
+      <c r="C241" s="1">
         <v>38.123260000000002</v>
       </c>
-      <c r="D241">
+      <c r="D241" s="1">
         <v>-122.05584</v>
       </c>
-      <c r="F241" t="s">
+      <c r="F241" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A242" t="s">
-        <v>6</v>
-      </c>
-      <c r="B242" t="s">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A242" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="C242">
+      <c r="C242" s="1">
         <v>38.106659999999998</v>
       </c>
-      <c r="D242">
+      <c r="D242" s="1">
         <v>-121.70219</v>
       </c>
-      <c r="F242" t="s">
+      <c r="F242" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A243" t="s">
-        <v>6</v>
-      </c>
-      <c r="B243" t="s">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A243" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B243" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C243">
+      <c r="C243" s="1">
         <v>38.069229999999997</v>
       </c>
-      <c r="D243">
+      <c r="D243" s="1">
         <v>-121.78117</v>
       </c>
-      <c r="F243" t="s">
+      <c r="F243" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A244" t="s">
-        <v>6</v>
-      </c>
-      <c r="B244" t="s">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A244" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B244" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C244">
+      <c r="C244" s="1">
         <v>38.071179999999998</v>
       </c>
-      <c r="D244">
+      <c r="D244" s="1">
         <v>-121.83995</v>
       </c>
-      <c r="F244" t="s">
+      <c r="F244" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A245" t="s">
-        <v>6</v>
-      </c>
-      <c r="B245" t="s">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A245" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B245" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C245">
+      <c r="C245" s="1">
         <v>38.079360000000001</v>
       </c>
-      <c r="D245">
+      <c r="D245" s="1">
         <v>-121.76155</v>
       </c>
-      <c r="F245" t="s">
+      <c r="F245" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A246" t="s">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A246" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B246" t="s">
+      <c r="B246" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="C246" s="1">
+      <c r="C246" s="3">
         <v>38.04598</v>
       </c>
-      <c r="D246" s="1">
+      <c r="D246" s="3">
         <v>-121.90991699999999</v>
       </c>
-      <c r="F246" t="s">
+      <c r="F246" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="G246" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A247" t="s">
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A247" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B247" t="s">
+      <c r="B247" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="C247" s="1">
+      <c r="C247" s="3">
         <v>38.047967</v>
       </c>
-      <c r="D247" s="1">
+      <c r="D247" s="3">
         <v>-121.90991699999999</v>
       </c>
-      <c r="F247" t="s">
+      <c r="F247" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="G247" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A248" t="s">
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A248" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B248" t="s">
+      <c r="B248" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C248" s="1">
+      <c r="C248" s="3">
         <v>38.042830000000002</v>
       </c>
-      <c r="D248" s="1">
+      <c r="D248" s="3">
         <v>-121.90991699999999</v>
       </c>
-      <c r="F248" t="s">
+      <c r="F248" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="G248" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A249" t="s">
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A249" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B249" t="s">
+      <c r="B249" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C249">
+      <c r="C249" s="1">
         <v>38.087969999999999</v>
       </c>
-      <c r="D249">
+      <c r="D249" s="1">
         <v>-121.74692</v>
       </c>
-      <c r="F249" t="s">
+      <c r="F249" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A250" t="s">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A250" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B250" t="s">
+      <c r="B250" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C250">
+      <c r="C250" s="1">
         <v>38.466259999999998</v>
       </c>
-      <c r="D250">
+      <c r="D250" s="1">
         <v>-121.58729</v>
       </c>
-      <c r="F250" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A251" t="s">
+      <c r="F250" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A251" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B251" t="s">
+      <c r="B251" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C251">
+      <c r="C251" s="1">
         <v>38.362259999999999</v>
       </c>
-      <c r="D251">
+      <c r="D251" s="1">
         <v>-121.63511</v>
       </c>
-      <c r="F251" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A252" t="s">
+      <c r="F251" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A252" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B252" t="s">
+      <c r="B252" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C252">
+      <c r="C252" s="1">
         <v>38.443109999999997</v>
       </c>
-      <c r="D252">
+      <c r="D252" s="1">
         <v>-121.59732</v>
       </c>
-      <c r="F252" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A253" t="s">
+      <c r="F252" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A253" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B253" t="s">
+      <c r="B253" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C253">
+      <c r="C253" s="1">
         <v>38.459670000000003</v>
       </c>
-      <c r="D253">
+      <c r="D253" s="1">
         <v>-121.59071</v>
       </c>
-      <c r="F253" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A254" t="s">
+      <c r="F253" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A254" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B254" t="s">
+      <c r="B254" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C254">
+      <c r="C254" s="1">
         <v>38.033679999999997</v>
       </c>
-      <c r="D254">
+      <c r="D254" s="1">
         <v>-121.83931</v>
       </c>
-      <c r="F254" t="s">
+      <c r="F254" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A255" t="s">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A255" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B255" t="s">
+      <c r="B255" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C255">
+      <c r="C255" s="1">
         <v>38.314839999999997</v>
       </c>
-      <c r="D255">
+      <c r="D255" s="1">
         <v>-121.65142</v>
       </c>
-      <c r="F255" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A256" t="s">
+      <c r="F255" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A256" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B256" t="s">
+      <c r="B256" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C256">
+      <c r="C256" s="1">
         <v>38.443530000000003</v>
       </c>
-      <c r="D256">
+      <c r="D256" s="1">
         <v>-121.59732</v>
       </c>
-      <c r="F256" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A257" t="s">
+      <c r="F256" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A257" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B257" t="s">
+      <c r="B257" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C257">
+      <c r="C257" s="1">
         <v>38.379800000000003</v>
       </c>
-      <c r="D257">
+      <c r="D257" s="1">
         <v>-121.62690000000001</v>
       </c>
-      <c r="F257" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A258" t="s">
+      <c r="F257" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A258" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B258" t="s">
+      <c r="B258" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C258">
+      <c r="C258" s="1">
         <v>38.375340000000001</v>
       </c>
-      <c r="D258">
+      <c r="D258" s="1">
         <v>-121.628</v>
       </c>
-      <c r="F258" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A259" t="s">
+      <c r="F258" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A259" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B259" t="s">
+      <c r="B259" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C259">
+      <c r="C259" s="1">
         <v>38.088320000000003</v>
       </c>
-      <c r="D259">
+      <c r="D259" s="1">
         <v>-121.74927</v>
       </c>
-      <c r="F259" t="s">
+      <c r="F259" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A260" t="s">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A260" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B260" t="s">
+      <c r="B260" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C260">
+      <c r="C260" s="1">
         <v>38.186390000000003</v>
       </c>
-      <c r="D260">
+      <c r="D260" s="1">
         <v>-121.98084</v>
       </c>
-      <c r="F260" t="s">
+      <c r="F260" s="1" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A261" t="s">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A261" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B261" t="s">
+      <c r="B261" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C261">
+      <c r="C261" s="1">
         <v>38.463549999999998</v>
       </c>
-      <c r="D261">
+      <c r="D261" s="1">
         <v>-121.58877</v>
       </c>
-      <c r="F261" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A262" t="s">
+      <c r="F261" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A262" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B262" t="s">
+      <c r="B262" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C262">
+      <c r="C262" s="1">
         <v>38.395130000000002</v>
       </c>
-      <c r="D262">
+      <c r="D262" s="1">
         <v>-121.61953</v>
       </c>
-      <c r="F262" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A263" t="s">
+      <c r="F262" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A263" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B263" t="s">
+      <c r="B263" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C263">
+      <c r="C263" s="1">
         <v>38.395130000000002</v>
       </c>
-      <c r="D263">
+      <c r="D263" s="1">
         <v>-121.61953</v>
       </c>
-      <c r="F263" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A264" t="s">
+      <c r="F263" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A264" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B264" t="s">
+      <c r="B264" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C264">
+      <c r="C264" s="1">
         <v>38.300849999999997</v>
       </c>
-      <c r="D264">
+      <c r="D264" s="1">
         <v>-121.65495</v>
       </c>
-      <c r="F264" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A265" t="s">
+      <c r="F264" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A265" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B265" t="s">
+      <c r="B265" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C265">
+      <c r="C265" s="1">
         <v>38.365270000000002</v>
       </c>
-      <c r="D265">
+      <c r="D265" s="1">
         <v>-121.63342</v>
       </c>
-      <c r="F265" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A266" t="s">
+      <c r="F265" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A266" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B266" t="s">
+      <c r="B266" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C266">
+      <c r="C266" s="1">
         <v>38.125950000000003</v>
       </c>
-      <c r="D266">
+      <c r="D266" s="1">
         <v>-122.00412</v>
       </c>
-      <c r="F266" t="s">
+      <c r="F266" s="1" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A267" t="s">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A267" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B267" t="s">
+      <c r="B267" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C267">
+      <c r="C267" s="1">
         <v>38.138120000000001</v>
       </c>
-      <c r="D267">
+      <c r="D267" s="1">
         <v>-122.03456</v>
       </c>
-      <c r="F267" t="s">
+      <c r="F267" s="1" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A268" t="s">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A268" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B268" t="s">
+      <c r="B268" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C268">
+      <c r="C268" s="1">
         <v>38.321720120000002</v>
       </c>
-      <c r="D268">
+      <c r="D268" s="1">
         <v>-121.65080639999999</v>
       </c>
-      <c r="F268" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A269" t="s">
+      <c r="F268" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A269" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B269">
+      <c r="B269" s="1">
         <v>405</v>
       </c>
-      <c r="C269">
+      <c r="C269" s="1">
         <v>38.033529999999999</v>
       </c>
-      <c r="D269">
+      <c r="D269" s="1">
         <v>-122.15815000000001</v>
       </c>
-      <c r="E269" t="s">
+      <c r="E269" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A270" t="s">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A270" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B270">
+      <c r="B270" s="1">
         <v>407</v>
       </c>
-      <c r="C270">
+      <c r="C270" s="1">
         <v>38.032980000000002</v>
       </c>
-      <c r="D270">
+      <c r="D270" s="1">
         <v>-122.14515</v>
       </c>
-      <c r="E270" t="s">
+      <c r="E270" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A271" t="s">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A271" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B271">
+      <c r="B271" s="1">
         <v>411</v>
       </c>
-      <c r="C271">
+      <c r="C271" s="1">
         <v>38.061169999999997</v>
       </c>
-      <c r="D271">
+      <c r="D271" s="1">
         <v>-122.06828</v>
       </c>
-      <c r="E271" t="s">
+      <c r="E271" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A272" t="s">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A272" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B272">
+      <c r="B272" s="1">
         <v>412</v>
       </c>
-      <c r="C272">
+      <c r="C272" s="1">
         <v>38.064619999999998</v>
       </c>
-      <c r="D272">
+      <c r="D272" s="1">
         <v>-122.06007</v>
       </c>
-      <c r="E272" t="s">
+      <c r="E272" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A273" t="s">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A273" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B273">
+      <c r="B273" s="1">
         <v>413</v>
       </c>
-      <c r="C273">
+      <c r="C273" s="1">
         <v>38.065950000000001</v>
       </c>
-      <c r="D273">
+      <c r="D273" s="1">
         <v>-122.04730000000001</v>
       </c>
-      <c r="E273" t="s">
+      <c r="E273" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A274" t="s">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A274" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B274">
+      <c r="B274" s="1">
         <v>416</v>
       </c>
-      <c r="C274">
+      <c r="C274" s="1">
         <v>38.0702</v>
       </c>
-      <c r="D274">
+      <c r="D274" s="1">
         <v>-122.09415</v>
       </c>
-      <c r="E274" t="s">
+      <c r="E274" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A275" t="s">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A275" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B275">
+      <c r="B275" s="1">
         <v>417</v>
       </c>
-      <c r="C275">
+      <c r="C275" s="1">
         <v>38.080750000000002</v>
       </c>
-      <c r="D275">
+      <c r="D275" s="1">
         <v>-122.083</v>
       </c>
-      <c r="E275" t="s">
+      <c r="E275" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A276" t="s">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A276" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B276">
+      <c r="B276" s="1">
         <v>501</v>
       </c>
-      <c r="C276">
+      <c r="C276" s="1">
         <v>38.061669999999999</v>
       </c>
-      <c r="D276">
+      <c r="D276" s="1">
         <v>-122.01955</v>
       </c>
-      <c r="E276" t="s">
+      <c r="E276" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A277" t="s">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A277" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B277">
+      <c r="B277" s="1">
         <v>502</v>
       </c>
-      <c r="C277">
+      <c r="C277" s="1">
         <v>38.05997</v>
       </c>
-      <c r="D277">
+      <c r="D277" s="1">
         <v>-122.00397</v>
       </c>
-      <c r="E277" t="s">
+      <c r="E277" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A278" t="s">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A278" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B278">
+      <c r="B278" s="1">
         <v>504</v>
       </c>
-      <c r="C278">
+      <c r="C278" s="1">
         <v>38.059449999999998</v>
       </c>
-      <c r="D278">
+      <c r="D278" s="1">
         <v>-121.97669999999999</v>
       </c>
-      <c r="E278" t="s">
+      <c r="E278" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A279" t="s">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A279" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B279">
+      <c r="B279" s="1">
         <v>505</v>
       </c>
-      <c r="C279">
+      <c r="C279" s="1">
         <v>38.057130000000001</v>
       </c>
-      <c r="D279">
+      <c r="D279" s="1">
         <v>-121.95596999999999</v>
       </c>
-      <c r="E279" t="s">
+      <c r="E279" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A280" t="s">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A280" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B280">
+      <c r="B280" s="1">
         <v>507</v>
       </c>
-      <c r="C280">
+      <c r="C280" s="1">
         <v>38.052280000000003</v>
       </c>
-      <c r="D280">
+      <c r="D280" s="1">
         <v>-121.93899999999999</v>
       </c>
-      <c r="E280" t="s">
+      <c r="E280" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A281" t="s">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A281" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B281">
+      <c r="B281" s="1">
         <v>508</v>
       </c>
-      <c r="C281">
+      <c r="C281" s="1">
         <v>38.04813</v>
       </c>
-      <c r="D281">
+      <c r="D281" s="1">
         <v>-121.91492</v>
       </c>
-      <c r="E281" t="s">
+      <c r="E281" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A282" t="s">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A282" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B282">
+      <c r="B282" s="1">
         <v>509</v>
       </c>
-      <c r="C282">
+      <c r="C282" s="1">
         <v>38.045470000000002</v>
       </c>
-      <c r="D282">
+      <c r="D282" s="1">
         <v>-121.90412000000001</v>
       </c>
-      <c r="E282" t="s">
+      <c r="E282" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A283" t="s">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A283" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B283">
+      <c r="B283" s="1">
         <v>510</v>
       </c>
-      <c r="C283">
+      <c r="C283" s="1">
         <v>38.048879999999997</v>
       </c>
-      <c r="D283">
+      <c r="D283" s="1">
         <v>-121.88782999999999</v>
       </c>
-      <c r="E283" t="s">
+      <c r="E283" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A284" t="s">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A284" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B284">
+      <c r="B284" s="1">
         <v>511</v>
       </c>
-      <c r="C284">
+      <c r="C284" s="1">
         <v>38.051299999999998</v>
       </c>
-      <c r="D284">
+      <c r="D284" s="1">
         <v>-121.88</v>
       </c>
-      <c r="E284" t="s">
+      <c r="E284" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A285" t="s">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A285" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B285">
+      <c r="B285" s="1">
         <v>512</v>
       </c>
-      <c r="C285">
+      <c r="C285" s="1">
         <v>38.056379999999997</v>
       </c>
-      <c r="D285">
+      <c r="D285" s="1">
         <v>-121.87721999999999</v>
       </c>
-      <c r="E285" t="s">
+      <c r="E285" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A286" t="s">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A286" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B286">
+      <c r="B286" s="1">
         <v>513</v>
       </c>
-      <c r="C286">
+      <c r="C286" s="1">
         <v>38.059199999999997</v>
       </c>
-      <c r="D286">
+      <c r="D286" s="1">
         <v>-121.86842</v>
       </c>
-      <c r="E286" t="s">
+      <c r="E286" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A287" t="s">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A287" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B287">
+      <c r="B287" s="1">
         <v>515</v>
       </c>
-      <c r="C287">
+      <c r="C287" s="1">
         <v>38.091999999999999</v>
       </c>
-      <c r="D287">
+      <c r="D287" s="1">
         <v>-122.01472</v>
       </c>
-      <c r="E287" t="s">
+      <c r="E287" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A288" t="s">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A288" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B288">
+      <c r="B288" s="1">
         <v>516</v>
       </c>
-      <c r="C288">
+      <c r="C288" s="1">
         <v>38.078670000000002</v>
       </c>
-      <c r="D288">
+      <c r="D288" s="1">
         <v>-121.99408</v>
       </c>
-      <c r="E288" t="s">
+      <c r="E288" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A289" t="s">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A289" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B289">
+      <c r="B289" s="1">
         <v>517</v>
       </c>
-      <c r="C289">
+      <c r="C289" s="1">
         <v>38.070219999999999</v>
       </c>
-      <c r="D289">
+      <c r="D289" s="1">
         <v>-121.97938000000001</v>
       </c>
-      <c r="E289" t="s">
+      <c r="E289" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A290" t="s">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A290" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B290">
+      <c r="B290" s="1">
         <v>518</v>
       </c>
-      <c r="C290">
+      <c r="C290" s="1">
         <v>38.068750000000001</v>
       </c>
-      <c r="D290">
+      <c r="D290" s="1">
         <v>-121.96802</v>
       </c>
-      <c r="E290" t="s">
+      <c r="E290" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A291" t="s">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A291" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B291">
+      <c r="B291" s="1">
         <v>519</v>
       </c>
-      <c r="C291">
+      <c r="C291" s="1">
         <v>38.073779999999999</v>
       </c>
-      <c r="D291">
+      <c r="D291" s="1">
         <v>-121.94725</v>
       </c>
-      <c r="E291" t="s">
+      <c r="E291" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A292" t="s">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A292" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B292">
+      <c r="B292" s="1">
         <v>601</v>
       </c>
-      <c r="C292">
+      <c r="C292" s="1">
         <v>38.103099999999998</v>
       </c>
-      <c r="D292">
+      <c r="D292" s="1">
         <v>-122.0356</v>
       </c>
-      <c r="E292" t="s">
+      <c r="E292" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A293" t="s">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A293" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B293">
+      <c r="B293" s="1">
         <v>602</v>
       </c>
-      <c r="C293">
+      <c r="C293" s="1">
         <v>38.117829999999998</v>
       </c>
-      <c r="D293">
+      <c r="D293" s="1">
         <v>-122.04183</v>
       </c>
-      <c r="E293" t="s">
+      <c r="E293" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A294" t="s">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A294" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B294">
+      <c r="B294" s="1">
         <v>603</v>
       </c>
-      <c r="C294">
+      <c r="C294" s="1">
         <v>38.115519999999997</v>
       </c>
-      <c r="D294">
+      <c r="D294" s="1">
         <v>-122.04805</v>
       </c>
-      <c r="E294" t="s">
+      <c r="E294" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A295" t="s">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A295" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B295">
+      <c r="B295" s="1">
         <v>605</v>
       </c>
-      <c r="C295">
+      <c r="C295" s="1">
         <v>38.148530000000001</v>
       </c>
-      <c r="D295">
+      <c r="D295" s="1">
         <v>-122.05737999999999</v>
       </c>
-      <c r="E295" t="s">
+      <c r="E295" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A296" t="s">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A296" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B296">
+      <c r="B296" s="1">
         <v>606</v>
       </c>
-      <c r="C296">
+      <c r="C296" s="1">
         <v>38.169800000000002</v>
       </c>
-      <c r="D296">
+      <c r="D296" s="1">
         <v>-122.02177</v>
       </c>
-      <c r="E296" t="s">
+      <c r="E296" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A297" t="s">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A297" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B297">
+      <c r="B297" s="1">
         <v>701</v>
       </c>
-      <c r="C297">
+      <c r="C297" s="1">
         <v>38.065049999999999</v>
       </c>
-      <c r="D297">
+      <c r="D297" s="1">
         <v>-121.83475</v>
       </c>
-      <c r="E297" t="s">
+      <c r="E297" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A298" t="s">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A298" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B298">
+      <c r="B298" s="1">
         <v>703</v>
       </c>
-      <c r="C298">
+      <c r="C298" s="1">
         <v>38.060870000000001</v>
       </c>
-      <c r="D298">
+      <c r="D298" s="1">
         <v>-121.79692</v>
       </c>
-      <c r="E298" t="s">
+      <c r="E298" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A299" t="s">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A299" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B299">
+      <c r="B299" s="1">
         <v>704</v>
       </c>
-      <c r="C299">
+      <c r="C299" s="1">
         <v>38.070869999999999</v>
       </c>
-      <c r="D299">
+      <c r="D299" s="1">
         <v>-121.77892</v>
       </c>
-      <c r="E299" t="s">
+      <c r="E299" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A300" t="s">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A300" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B300">
+      <c r="B300" s="1">
         <v>705</v>
       </c>
-      <c r="C300">
+      <c r="C300" s="1">
         <v>38.079250000000002</v>
       </c>
-      <c r="D300">
+      <c r="D300" s="1">
         <v>-121.76179999999999</v>
       </c>
-      <c r="E300" t="s">
+      <c r="E300" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A301" t="s">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A301" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B301">
+      <c r="B301" s="1">
         <v>706</v>
       </c>
-      <c r="C301">
+      <c r="C301" s="1">
         <v>38.090299999999999</v>
       </c>
-      <c r="D301">
+      <c r="D301" s="1">
         <v>-121.74</v>
       </c>
-      <c r="E301" t="s">
+      <c r="E301" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A302" t="s">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A302" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B302">
+      <c r="B302" s="1">
         <v>715</v>
       </c>
-      <c r="C302">
+      <c r="C302" s="1">
         <v>38.222949999999997</v>
       </c>
-      <c r="D302">
+      <c r="D302" s="1">
         <v>-121.67362</v>
       </c>
-      <c r="E302" t="s">
+      <c r="E302" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A303" t="s">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A303" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B303">
+      <c r="B303" s="1">
         <v>716</v>
       </c>
-      <c r="C303">
+      <c r="C303" s="1">
         <v>38.237870000000001</v>
       </c>
-      <c r="D303">
+      <c r="D303" s="1">
         <v>-121.68438</v>
       </c>
-      <c r="E303" t="s">
+      <c r="E303" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A304" t="s">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A304" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B304">
+      <c r="B304" s="1">
         <v>719</v>
       </c>
-      <c r="C304">
+      <c r="C304" s="1">
         <v>38.33428</v>
       </c>
-      <c r="D304">
+      <c r="D304" s="1">
         <v>-121.64733</v>
       </c>
-      <c r="E304" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A305" t="s">
+      <c r="E304" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A305" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B305">
+      <c r="B305" s="1">
         <v>721</v>
       </c>
-      <c r="C305">
+      <c r="C305" s="1">
         <v>38.268149999999999</v>
       </c>
-      <c r="D305">
+      <c r="D305" s="1">
         <v>-121.70277</v>
       </c>
-      <c r="E305" t="s">
+      <c r="E305" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A306" t="s">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A306" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B306">
+      <c r="B306" s="1">
         <v>796</v>
       </c>
-      <c r="C306">
+      <c r="C306" s="1">
         <v>38.473869999999998</v>
       </c>
-      <c r="D306">
+      <c r="D306" s="1">
         <v>-121.5844</v>
       </c>
-      <c r="E306" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A307" t="s">
+      <c r="E306" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A307" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B307">
+      <c r="B307" s="1">
         <v>797</v>
       </c>
-      <c r="C307">
+      <c r="C307" s="1">
         <v>38.404620000000001</v>
       </c>
-      <c r="D307">
+      <c r="D307" s="1">
         <v>-121.6156</v>
       </c>
-      <c r="E307" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A308" t="s">
+      <c r="E307" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A308" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B308">
+      <c r="B308" s="1">
         <v>802</v>
       </c>
-      <c r="C308">
+      <c r="C308" s="1">
         <v>38.03528</v>
       </c>
-      <c r="D308">
+      <c r="D308" s="1">
         <v>-121.83875</v>
       </c>
-      <c r="E308" t="s">
+      <c r="E308" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A309" t="s">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A309" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B309">
+      <c r="B309" s="1">
         <v>806</v>
       </c>
-      <c r="C309">
+      <c r="C309" s="1">
         <v>38.02872</v>
       </c>
-      <c r="D309">
+      <c r="D309" s="1">
         <v>-121.7617</v>
       </c>
-      <c r="E309" t="s">
+      <c r="E309" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A310" t="s">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A310" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B310">
+      <c r="B310" s="1">
         <v>807</v>
       </c>
-      <c r="C310">
+      <c r="C310" s="1">
         <v>38.029949999999999</v>
       </c>
-      <c r="D310">
+      <c r="D310" s="1">
         <v>-121.73202999999999</v>
       </c>
-      <c r="E310" t="s">
+      <c r="E310" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A311" t="s">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A311" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B311">
+      <c r="B311" s="1">
         <v>340</v>
       </c>
-      <c r="C311">
+      <c r="C311" s="1">
         <v>38.09928</v>
       </c>
-      <c r="D311">
+      <c r="D311" s="1">
         <v>-122.26344</v>
       </c>
-      <c r="E311" t="s">
+      <c r="E311" s="1" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A312" t="s">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A312" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B312">
+      <c r="B312" s="1">
         <v>405</v>
       </c>
-      <c r="C312">
+      <c r="C312" s="1">
         <v>38.03969</v>
       </c>
-      <c r="D312">
+      <c r="D312" s="1">
         <v>-122.15049999999999</v>
       </c>
-      <c r="E312" t="s">
+      <c r="E312" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A313" t="s">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A313" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B313">
+      <c r="B313" s="1">
         <v>411</v>
       </c>
-      <c r="C313">
+      <c r="C313" s="1">
         <v>38.051310000000001</v>
       </c>
-      <c r="D313">
+      <c r="D313" s="1">
         <v>-122.08331</v>
       </c>
-      <c r="E313" t="s">
+      <c r="E313" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A314" t="s">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A314" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B314">
+      <c r="B314" s="1">
         <v>418</v>
       </c>
-      <c r="C314">
+      <c r="C314" s="1">
         <v>38.064810000000001</v>
       </c>
-      <c r="D314">
+      <c r="D314" s="1">
         <v>-122.09781</v>
       </c>
-      <c r="E314" t="s">
+      <c r="E314" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A315" t="s">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A315" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B315">
+      <c r="B315" s="1">
         <v>501</v>
       </c>
-      <c r="C315">
+      <c r="C315" s="1">
         <v>38.07338</v>
       </c>
-      <c r="D315">
+      <c r="D315" s="1">
         <v>-122.02246</v>
       </c>
-      <c r="E315" t="s">
+      <c r="E315" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A316" t="s">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A316" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B316">
+      <c r="B316" s="1">
         <v>504</v>
       </c>
-      <c r="C316">
+      <c r="C316" s="1">
         <v>38.061059999999998</v>
       </c>
-      <c r="D316">
+      <c r="D316" s="1">
         <v>-122.01372000000001</v>
       </c>
-      <c r="E316" t="s">
+      <c r="E316" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A317" t="s">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A317" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B317">
+      <c r="B317" s="1">
         <v>508</v>
       </c>
-      <c r="C317">
+      <c r="C317" s="1">
         <v>38.045499999999997</v>
       </c>
-      <c r="D317">
+      <c r="D317" s="1">
         <v>-121.91880999999999</v>
       </c>
-      <c r="E317" t="s">
+      <c r="E317" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A318" t="s">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A318" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B318">
+      <c r="B318" s="1">
         <v>513</v>
       </c>
-      <c r="C318">
+      <c r="C318" s="1">
         <v>38.058309999999999</v>
       </c>
-      <c r="D318">
+      <c r="D318" s="1">
         <v>-121.86799999999999</v>
       </c>
-      <c r="E318" t="s">
+      <c r="E318" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A319" t="s">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A319" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B319">
+      <c r="B319" s="1">
         <v>519</v>
       </c>
-      <c r="C319">
+      <c r="C319" s="1">
         <v>38.072310000000002</v>
       </c>
-      <c r="D319">
+      <c r="D319" s="1">
         <v>-121.95968999999999</v>
       </c>
-      <c r="E319" t="s">
+      <c r="E319" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A320" t="s">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A320" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B320">
+      <c r="B320" s="1">
         <v>520</v>
       </c>
-      <c r="C320">
+      <c r="C320" s="1">
         <v>38.032809999999998</v>
       </c>
-      <c r="D320">
+      <c r="D320" s="1">
         <v>-121.86931</v>
       </c>
-      <c r="E320" t="s">
+      <c r="E320" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A321" t="s">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A321" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B321">
+      <c r="B321" s="1">
         <v>602</v>
       </c>
-      <c r="C321">
+      <c r="C321" s="1">
         <v>38.113999999999997</v>
       </c>
-      <c r="D321">
+      <c r="D321" s="1">
         <v>-122.04619</v>
       </c>
-      <c r="E321" t="s">
+      <c r="E321" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A322" t="s">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A322" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B322">
+      <c r="B322" s="1">
         <v>606</v>
       </c>
-      <c r="C322">
+      <c r="C322" s="1">
         <v>38.169469999999997</v>
       </c>
-      <c r="D322">
+      <c r="D322" s="1">
         <v>-122.02567000000001</v>
       </c>
-      <c r="E322" t="s">
+      <c r="E322" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A323" t="s">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A323" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B323">
+      <c r="B323" s="1">
         <v>609</v>
       </c>
-      <c r="C323">
+      <c r="C323" s="1">
         <v>38.167189999999998</v>
       </c>
-      <c r="D323">
+      <c r="D323" s="1">
         <v>-121.938</v>
       </c>
-      <c r="E323" t="s">
+      <c r="E323" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A324" t="s">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A324" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B324">
+      <c r="B324" s="1">
         <v>610</v>
       </c>
-      <c r="C324">
+      <c r="C324" s="1">
         <v>38.118810000000003</v>
       </c>
-      <c r="D324">
+      <c r="D324" s="1">
         <v>-121.88919</v>
       </c>
-      <c r="E324" t="s">
+      <c r="E324" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A325" t="s">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A325" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B325">
+      <c r="B325" s="1">
         <v>701</v>
       </c>
-      <c r="C325">
+      <c r="C325" s="1">
         <v>38.065638999999997</v>
       </c>
-      <c r="D325">
+      <c r="D325" s="1">
         <v>-121.834694</v>
       </c>
-      <c r="E325" t="s">
+      <c r="E325" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A326" t="s">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A326" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B326">
+      <c r="B326" s="1">
         <v>703</v>
       </c>
-      <c r="C326">
+      <c r="C326" s="1">
         <v>38.063139</v>
       </c>
-      <c r="D326">
+      <c r="D326" s="1">
         <v>-121.796083</v>
       </c>
-      <c r="E326" t="s">
+      <c r="E326" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A327" t="s">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A327" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B327">
+      <c r="B327" s="1">
         <v>704</v>
       </c>
-      <c r="C327">
+      <c r="C327" s="1">
         <v>38.06917</v>
       </c>
-      <c r="D327">
+      <c r="D327" s="1">
         <v>-121.77528</v>
       </c>
-      <c r="E327" t="s">
+      <c r="E327" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A328" t="s">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A328" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B328">
+      <c r="B328" s="1">
         <v>705</v>
       </c>
-      <c r="C328">
+      <c r="C328" s="1">
         <v>38.079611</v>
       </c>
-      <c r="D328">
+      <c r="D328" s="1">
         <v>-121.761472</v>
       </c>
-      <c r="E328" t="s">
+      <c r="E328" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A329" t="s">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A329" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B329">
+      <c r="B329" s="1">
         <v>706</v>
       </c>
-      <c r="C329">
+      <c r="C329" s="1">
         <v>38.085189999999997</v>
       </c>
-      <c r="D329">
+      <c r="D329" s="1">
         <v>-121.75069000000001</v>
       </c>
-      <c r="E329" t="s">
+      <c r="E329" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A330" t="s">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A330" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B330">
+      <c r="B330" s="1">
         <v>707</v>
       </c>
-      <c r="C330">
+      <c r="C330" s="1">
         <v>38.113500000000002</v>
       </c>
-      <c r="D330">
+      <c r="D330" s="1">
         <v>-121.7075</v>
       </c>
-      <c r="E330" t="s">
+      <c r="E330" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A331" t="s">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A331" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B331">
+      <c r="B331" s="1">
         <v>711</v>
       </c>
-      <c r="C331">
+      <c r="C331" s="1">
         <v>38.178809999999999</v>
       </c>
-      <c r="D331">
+      <c r="D331" s="1">
         <v>-121.66531000000001</v>
       </c>
-      <c r="E331" t="s">
+      <c r="E331" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A332" t="s">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A332" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B332">
+      <c r="B332" s="1">
         <v>712</v>
       </c>
-      <c r="C332">
+      <c r="C332" s="1">
         <v>38.190420000000003</v>
       </c>
-      <c r="D332">
+      <c r="D332" s="1">
         <v>-121.64095</v>
       </c>
-      <c r="E332" t="s">
+      <c r="E332" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A333" t="s">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A333" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B333">
+      <c r="B333" s="1">
         <v>713</v>
       </c>
-      <c r="C333">
+      <c r="C333" s="1">
         <v>38.207120000000003</v>
       </c>
-      <c r="D333">
+      <c r="D333" s="1">
         <v>-121.66007999999999</v>
       </c>
-      <c r="E333" t="s">
+      <c r="E333" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A334" t="s">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A334" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B334">
+      <c r="B334" s="1">
         <v>715</v>
       </c>
-      <c r="C334">
+      <c r="C334" s="1">
         <v>38.222949999999997</v>
       </c>
-      <c r="D334">
+      <c r="D334" s="1">
         <v>-121.67362</v>
       </c>
-      <c r="E334" t="s">
+      <c r="E334" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A335" t="s">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A335" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B335">
+      <c r="B335" s="1">
         <v>716</v>
       </c>
-      <c r="C335">
+      <c r="C335" s="1">
         <v>38.258279999999999</v>
       </c>
-      <c r="D335">
+      <c r="D335" s="1">
         <v>-121.69164000000001</v>
       </c>
-      <c r="E335" t="s">
+      <c r="E335" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A336" t="s">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A336" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B336">
+      <c r="B336" s="1">
         <v>719</v>
       </c>
-      <c r="C336">
+      <c r="C336" s="1">
         <v>38.33428</v>
       </c>
-      <c r="D336">
+      <c r="D336" s="1">
         <v>-121.64733</v>
       </c>
-      <c r="E336" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A337" t="s">
+      <c r="E336" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A337" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B337">
+      <c r="B337" s="1">
         <v>801</v>
       </c>
-      <c r="C337">
+      <c r="C337" s="1">
         <v>38.043689999999998</v>
       </c>
-      <c r="D337">
+      <c r="D337" s="1">
         <v>-121.84399999999999</v>
       </c>
-      <c r="E337" t="s">
+      <c r="E337" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A338" t="s">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A338" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B338">
+      <c r="B338" s="1">
         <v>804</v>
       </c>
-      <c r="C338">
+      <c r="C338" s="1">
         <v>38.018189999999997</v>
       </c>
-      <c r="D338">
+      <c r="D338" s="1">
         <v>-121.797</v>
       </c>
-      <c r="E338" t="s">
+      <c r="E338" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A339" t="s">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A339" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B339">
+      <c r="B339" s="1">
         <v>340</v>
       </c>
-      <c r="C339">
+      <c r="C339" s="1">
         <v>38.103909999999999</v>
       </c>
-      <c r="D339">
+      <c r="D339" s="1">
         <v>-122.26945000000001</v>
       </c>
-      <c r="E339" t="s">
+      <c r="E339" s="1" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A340" t="s">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A340" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B340">
+      <c r="B340" s="1">
         <v>405</v>
       </c>
-      <c r="C340">
+      <c r="C340" s="1">
         <v>38.038060000000002</v>
       </c>
-      <c r="D340">
+      <c r="D340" s="1">
         <v>-122.15049999999999</v>
       </c>
-      <c r="E340" t="s">
+      <c r="E340" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A341" t="s">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A341" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B341">
+      <c r="B341" s="1">
         <v>418</v>
       </c>
-      <c r="C341">
+      <c r="C341" s="1">
         <v>38.064810000000001</v>
       </c>
-      <c r="D341">
+      <c r="D341" s="1">
         <v>-122.09781</v>
       </c>
-      <c r="E341" t="s">
+      <c r="E341" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A342" t="s">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A342" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B342">
+      <c r="B342" s="1">
         <v>501</v>
       </c>
-      <c r="C342">
+      <c r="C342" s="1">
         <v>38.07338</v>
       </c>
-      <c r="D342">
+      <c r="D342" s="1">
         <v>-122.02246</v>
       </c>
-      <c r="E342" t="s">
+      <c r="E342" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A343" t="s">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A343" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B343">
+      <c r="B343" s="1">
         <v>508</v>
       </c>
-      <c r="C343">
+      <c r="C343" s="1">
         <v>38.045560000000002</v>
       </c>
-      <c r="D343">
+      <c r="D343" s="1">
         <v>-121.923</v>
       </c>
-      <c r="E343" t="s">
+      <c r="E343" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A344" t="s">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A344" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B344">
+      <c r="B344" s="1">
         <v>513</v>
       </c>
-      <c r="C344">
+      <c r="C344" s="1">
         <v>38.059460000000001</v>
       </c>
-      <c r="D344">
+      <c r="D344" s="1">
         <v>-121.864</v>
       </c>
-      <c r="E344" t="s">
+      <c r="E344" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A345" t="s">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A345" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B345">
+      <c r="B345" s="1">
         <v>519</v>
       </c>
-      <c r="C345">
+      <c r="C345" s="1">
         <v>38.072310000000002</v>
       </c>
-      <c r="D345">
+      <c r="D345" s="1">
         <v>-121.95968999999999</v>
       </c>
-      <c r="E345" t="s">
+      <c r="E345" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A346" t="s">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A346" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B346">
+      <c r="B346" s="1">
         <v>520</v>
       </c>
-      <c r="C346">
+      <c r="C346" s="1">
         <v>38.032809999999998</v>
       </c>
-      <c r="D346">
+      <c r="D346" s="1">
         <v>-121.86931</v>
       </c>
-      <c r="E346" t="s">
+      <c r="E346" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A347" t="s">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A347" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B347">
+      <c r="B347" s="1">
         <v>602</v>
       </c>
-      <c r="C347">
+      <c r="C347" s="1">
         <v>38.113999999999997</v>
       </c>
-      <c r="D347">
+      <c r="D347" s="1">
         <v>-122.04619</v>
       </c>
-      <c r="E347" t="s">
+      <c r="E347" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A348" t="s">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A348" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B348">
+      <c r="B348" s="1">
         <v>606</v>
       </c>
-      <c r="C348">
+      <c r="C348" s="1">
         <v>38.167760000000001</v>
       </c>
-      <c r="D348">
+      <c r="D348" s="1">
         <v>-122.02200999999999</v>
       </c>
-      <c r="E348" t="s">
+      <c r="E348" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A349" t="s">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A349" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B349">
+      <c r="B349" s="1">
         <v>609</v>
       </c>
-      <c r="C349">
+      <c r="C349" s="1">
         <v>38.167189999999998</v>
       </c>
-      <c r="D349">
+      <c r="D349" s="1">
         <v>-121.938</v>
       </c>
-      <c r="E349" t="s">
+      <c r="E349" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A350" t="s">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A350" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B350">
+      <c r="B350" s="1">
         <v>610</v>
       </c>
-      <c r="C350">
+      <c r="C350" s="1">
         <v>38.118810000000003</v>
       </c>
-      <c r="D350">
+      <c r="D350" s="1">
         <v>-121.88919</v>
       </c>
-      <c r="E350" t="s">
+      <c r="E350" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A351" t="s">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A351" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B351">
+      <c r="B351" s="1">
         <v>704</v>
       </c>
-      <c r="C351">
+      <c r="C351" s="1">
         <v>38.06776</v>
       </c>
-      <c r="D351">
+      <c r="D351" s="1">
         <v>-121.77500999999999</v>
       </c>
-      <c r="E351" t="s">
+      <c r="E351" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A352" t="s">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A352" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B352">
+      <c r="B352" s="1">
         <v>706</v>
       </c>
-      <c r="C352">
+      <c r="C352" s="1">
         <v>38.090060000000001</v>
       </c>
-      <c r="D352">
+      <c r="D352" s="1">
         <v>-121.739</v>
       </c>
-      <c r="E352" t="s">
+      <c r="E352" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A353" t="s">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A353" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B353">
+      <c r="B353" s="1">
         <v>707</v>
       </c>
-      <c r="C353">
+      <c r="C353" s="1">
         <v>38.112259999999999</v>
       </c>
-      <c r="D353">
+      <c r="D353" s="1">
         <v>-121.70601000000001</v>
       </c>
-      <c r="E353" t="s">
+      <c r="E353" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A354" t="s">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A354" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B354">
+      <c r="B354" s="1">
         <v>713</v>
       </c>
-      <c r="C354">
+      <c r="C354" s="1">
         <v>38.207120000000003</v>
       </c>
-      <c r="D354">
+      <c r="D354" s="1">
         <v>-121.66007999999999</v>
       </c>
-      <c r="E354" t="s">
+      <c r="E354" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A355" t="s">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A355" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B355">
+      <c r="B355" s="1">
         <v>716</v>
       </c>
-      <c r="C355">
+      <c r="C355" s="1">
         <v>38.237870000000001</v>
       </c>
-      <c r="D355">
+      <c r="D355" s="1">
         <v>-121.68438</v>
       </c>
-      <c r="E355" t="s">
+      <c r="E355" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A356" t="s">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A356" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B356">
+      <c r="B356" s="1">
         <v>719</v>
       </c>
-      <c r="C356">
+      <c r="C356" s="1">
         <v>38.33428</v>
       </c>
-      <c r="D356">
+      <c r="D356" s="1">
         <v>-121.64733</v>
       </c>
-      <c r="E356" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A357" t="s">
+      <c r="E356" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A357" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B357">
+      <c r="B357" s="1">
         <v>721</v>
       </c>
-      <c r="C357">
+      <c r="C357" s="1">
         <v>38.268149999999999</v>
       </c>
-      <c r="D357">
+      <c r="D357" s="1">
         <v>-121.70277</v>
       </c>
-      <c r="E357" t="s">
+      <c r="E357" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A358" t="s">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A358" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B358">
+      <c r="B358" s="1">
         <v>723</v>
       </c>
-      <c r="C358">
+      <c r="C358" s="1">
         <v>38.236150000000002</v>
       </c>
-      <c r="D358">
+      <c r="D358" s="1">
         <v>-121.67348</v>
       </c>
-      <c r="E358" t="s">
+      <c r="E358" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A359" t="s">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A359" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B359">
+      <c r="B359" s="1">
         <v>795</v>
       </c>
-      <c r="C359">
+      <c r="C359" s="1">
         <v>38.537700000000001</v>
       </c>
-      <c r="D359">
+      <c r="D359" s="1">
         <v>-121.58468000000001</v>
       </c>
-      <c r="E359" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A360" t="s">
+      <c r="E359" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A360" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B360">
+      <c r="B360" s="1">
         <v>797</v>
       </c>
-      <c r="C360">
+      <c r="C360" s="1">
         <v>38.404620000000001</v>
       </c>
-      <c r="D360">
+      <c r="D360" s="1">
         <v>-121.6156</v>
       </c>
-      <c r="E360" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A361" t="s">
+      <c r="E360" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A361" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B361">
+      <c r="B361" s="1">
         <v>801</v>
       </c>
-      <c r="C361">
+      <c r="C361" s="1">
         <v>38.055610000000001</v>
       </c>
-      <c r="D361">
+      <c r="D361" s="1">
         <v>-121.84699999999999</v>
       </c>
-      <c r="E361" t="s">
+      <c r="E361" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A362" t="s">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A362" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B362">
+      <c r="B362" s="1">
         <v>804</v>
       </c>
-      <c r="C362">
+      <c r="C362" s="1">
         <v>38.020560000000003</v>
       </c>
-      <c r="D362">
+      <c r="D362" s="1">
         <v>-121.794</v>
       </c>
-      <c r="E362" t="s">
+      <c r="E362" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A363" t="s">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A363" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B363">
+      <c r="B363" s="1">
         <v>797</v>
       </c>
-      <c r="C363">
+      <c r="C363" s="1">
         <v>38.404221999999997</v>
       </c>
-      <c r="D363">
+      <c r="D363" s="1">
         <v>-121.615639</v>
       </c>
-      <c r="E363" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A364" t="s">
+      <c r="E363" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A364" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B364">
+      <c r="B364" s="1">
         <v>704</v>
       </c>
-      <c r="C364">
+      <c r="C364" s="1">
         <v>38.071778000000002</v>
       </c>
-      <c r="D364">
+      <c r="D364" s="1">
         <v>-121.77975000000001</v>
       </c>
-      <c r="E364" t="s">
+      <c r="E364" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A365" t="s">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A365" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B365">
+      <c r="B365" s="1">
         <v>705</v>
       </c>
-      <c r="C365">
+      <c r="C365" s="1">
         <v>38.080638999999998</v>
       </c>
-      <c r="D365">
+      <c r="D365" s="1">
         <v>-121.760194</v>
       </c>
-      <c r="E365" t="s">
+      <c r="E365" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A366" t="s">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A366" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B366">
+      <c r="B366" s="1">
         <v>706</v>
       </c>
-      <c r="C366">
+      <c r="C366" s="1">
         <v>38.093860999999997</v>
       </c>
-      <c r="D366">
+      <c r="D366" s="1">
         <v>-121.7375</v>
       </c>
-      <c r="E366" t="s">
+      <c r="E366" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A367" t="s">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A367" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B367" t="s">
+      <c r="B367" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C367">
+      <c r="C367" s="1">
         <v>37.815818999999998</v>
       </c>
-      <c r="D367">
+      <c r="D367" s="1">
         <v>-121.558995</v>
       </c>
-      <c r="E367" t="s">
+      <c r="E367" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A368" t="s">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A368" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B368" t="s">
+      <c r="B368" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="C368">
+      <c r="C368" s="1">
         <v>37.825671</v>
       </c>
-      <c r="D368">
+      <c r="D368" s="1">
         <v>-121.596789</v>
       </c>
-      <c r="E368" t="s">
+      <c r="E368" s="1" t="s">
         <v>301</v>
       </c>
     </row>
